--- a/08 DE MARZO DE 2026.xlsx
+++ b/08 DE MARZO DE 2026.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan_\Downloads\programa gemini original\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9C4B85-4BCB-4F89-9A38-5B469D3F582E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="08-03-26" sheetId="1" r:id="rId1"/>
@@ -1947,8 +1953,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="32">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2438,7 +2444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2527,14 +2533,72 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2543,91 +2607,155 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2638,163 +2766,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2833,7 +2809,7 @@
         <xdr:cNvPr id="6" name="Texto 332">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53871877-B185-46BD-B0BF-A2497264DB32}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53871877-B185-46BD-B0BF-A2497264DB32}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2922,7 +2898,7 @@
         <xdr:cNvPr id="7" name="Texto 466">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75FA6B1B-1476-47E2-A7DE-8A81786133B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75FA6B1B-1476-47E2-A7DE-8A81786133B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3001,7 +2977,7 @@
         <xdr:cNvPr id="8" name="1 Imagen">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F560F2D-7011-478E-BD6C-CCEEB87B3CCF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F560F2D-7011-478E-BD6C-CCEEB87B3CCF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3076,7 +3052,7 @@
         <xdr:cNvPr id="9" name="Texto 466">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E3D7913-313E-4136-B4FD-273E00CC7FF0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E3D7913-313E-4136-B4FD-273E00CC7FF0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3157,7 +3133,7 @@
         <xdr:cNvPr id="11" name="54 CuadroTexto">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3977A2F-5BFB-498F-A815-A93B0AB44DB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3977A2F-5BFB-498F-A815-A93B0AB44DB9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3506,7 +3482,7 @@
         <xdr:cNvPr id="12" name="7 Imagen">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DE953AA-A2E1-45C3-9600-4CC93883E5EB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DE953AA-A2E1-45C3-9600-4CC93883E5EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3580,7 +3556,7 @@
         <xdr:cNvPr id="13" name="10 Imagen">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E842F99-C360-469C-951A-041031EF6AAD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E842F99-C360-469C-951A-041031EF6AAD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3923,69 +3899,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J268"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.140625" customWidth="1"/>
-    <col min="2" max="2" width="3.85546875" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" customWidth="1"/>
+    <col min="2" max="2" width="3.88671875" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" customWidth="1"/>
+    <col min="4" max="4" width="5.109375" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.75">
+    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.6">
       <c r="A1" s="13"/>
       <c r="B1" s="14"/>
-      <c r="C1" s="115" t="s">
+      <c r="C1" s="69" t="s">
         <v>238</v>
       </c>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="116"/>
-    </row>
-    <row r="2" spans="1:10" ht="28.5" thickBot="1">
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="70"/>
+    </row>
+    <row r="2" spans="1:10" ht="27.6" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A2" s="15"/>
       <c r="B2" s="16"/>
-      <c r="C2" s="117" t="s">
+      <c r="C2" s="71" t="s">
         <v>241</v>
       </c>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="118"/>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="72"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="18"/>
-      <c r="C3" s="119" t="s">
+      <c r="C3" s="73" t="s">
         <v>180</v>
       </c>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119" t="s">
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119" t="s">
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73" t="s">
         <v>175</v>
       </c>
-      <c r="J3" s="120"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="74"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>181</v>
       </c>
@@ -3993,49 +3969,49 @@
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
       <c r="E4" s="21"/>
-      <c r="F4" s="121" t="s">
+      <c r="F4" s="75" t="s">
         <v>176</v>
       </c>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121" t="s">
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="J4" s="122"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="123" t="s">
+      <c r="J4" s="76"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="77" t="s">
         <v>182</v>
       </c>
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="121" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="75" t="s">
         <v>178</v>
       </c>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="126"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A6" s="127" t="s">
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="80"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="49" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="128"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="129" t="s">
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="G6" s="129"/>
-      <c r="H6" s="129"/>
-      <c r="I6" s="129"/>
-      <c r="J6" s="130"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="52"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="22"/>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -4047,7 +4023,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
       <c r="B8" s="26"/>
       <c r="C8" s="26"/>
@@ -4059,7 +4035,7 @@
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="22"/>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -4071,7 +4047,7 @@
       <c r="I9" s="23"/>
       <c r="J9" s="28"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
@@ -4083,7 +4059,7 @@
       <c r="I10" s="23"/>
       <c r="J10" s="28"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="22"/>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -4095,7 +4071,7 @@
       <c r="I11" s="23"/>
       <c r="J11" s="28"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -4107,7 +4083,7 @@
       <c r="I12" s="23"/>
       <c r="J12" s="28"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="22"/>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
@@ -4119,7 +4095,7 @@
       <c r="I13" s="23"/>
       <c r="J13" s="28"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="22"/>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -4131,86 +4107,86 @@
       <c r="I14" s="23"/>
       <c r="J14" s="28"/>
     </row>
-    <row r="15" spans="1:10" ht="6" customHeight="1"/>
-    <row r="16" spans="1:10" ht="18" customHeight="1">
-      <c r="A16" s="66" t="s">
+    <row r="15" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="63" t="s">
+      <c r="B16" s="54"/>
+      <c r="C16" s="68" t="s">
         <v>597</v>
       </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
       <c r="J16" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-    </row>
-    <row r="18" spans="1:10" ht="11.25" customHeight="1">
-      <c r="A18" s="96" t="s">
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+    </row>
+    <row r="18" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-    </row>
-    <row r="19" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A19" s="92" t="s">
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+    </row>
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="64" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="89" t="s">
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="91" t="s">
         <v>184</v>
       </c>
-      <c r="J19" s="64"/>
-    </row>
-    <row r="20" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A20" s="92" t="s">
+      <c r="J19" s="54"/>
+    </row>
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="89" t="s">
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="64"/>
-    </row>
-    <row r="21" spans="1:10" ht="18" customHeight="1">
+      <c r="J20" s="54"/>
+    </row>
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>4</v>
       </c>
@@ -4229,10 +4205,10 @@
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G21" s="75" t="s">
+      <c r="G21" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="75"/>
+      <c r="H21" s="85"/>
       <c r="I21" s="2" t="s">
         <v>11</v>
       </c>
@@ -4240,8 +4216,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="18" customHeight="1">
-      <c r="A22" s="49" t="s">
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="38" t="s">
         <v>248</v>
       </c>
       <c r="B22" s="4">
@@ -4253,16 +4229,16 @@
       <c r="D22" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="46" t="s">
+      <c r="E22" s="30" t="s">
         <v>200</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="70" t="s">
+      <c r="G22" s="58" t="s">
         <v>246</v>
       </c>
-      <c r="H22" s="71"/>
+      <c r="H22" s="59"/>
       <c r="I22" s="7" t="s">
         <v>224</v>
       </c>
@@ -4270,7 +4246,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="18" customHeight="1">
+    <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>255</v>
       </c>
@@ -4289,10 +4265,10 @@
       <c r="F23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G23" s="70" t="s">
+      <c r="G23" s="58" t="s">
         <v>252</v>
       </c>
-      <c r="H23" s="71"/>
+      <c r="H23" s="59"/>
       <c r="I23" s="7" t="s">
         <v>253</v>
       </c>
@@ -4300,7 +4276,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1">
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>0</v>
       </c>
@@ -4319,10 +4295,10 @@
       <c r="F24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="70" t="s">
+      <c r="G24" s="58" t="s">
         <v>259</v>
       </c>
-      <c r="H24" s="71"/>
+      <c r="H24" s="59"/>
       <c r="I24" s="7" t="s">
         <v>608</v>
       </c>
@@ -4330,7 +4306,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="18" customHeight="1">
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>261</v>
       </c>
@@ -4343,16 +4319,16 @@
       <c r="D25" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="30" t="s">
         <v>364</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="70" t="s">
+      <c r="G25" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="H25" s="71"/>
+      <c r="H25" s="59"/>
       <c r="I25" s="7" t="s">
         <v>67</v>
       </c>
@@ -4360,7 +4336,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="18" customHeight="1">
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>263</v>
       </c>
@@ -4373,16 +4349,16 @@
       <c r="D26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="30" t="s">
         <v>560</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G26" s="70" t="s">
+      <c r="G26" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="H26" s="71"/>
+      <c r="H26" s="59"/>
       <c r="I26" s="7" t="s">
         <v>49</v>
       </c>
@@ -4390,7 +4366,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="18" customHeight="1">
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>267</v>
       </c>
@@ -4409,10 +4385,10 @@
       <c r="F27" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G27" s="70" t="s">
+      <c r="G27" s="58" t="s">
         <v>266</v>
       </c>
-      <c r="H27" s="71"/>
+      <c r="H27" s="59"/>
       <c r="I27" s="7" t="s">
         <v>22</v>
       </c>
@@ -4420,7 +4396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1" thickBot="1">
+    <row r="28" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>270</v>
       </c>
@@ -4439,10 +4415,10 @@
       <c r="F28" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="107" t="s">
+      <c r="G28" s="94" t="s">
         <v>272</v>
       </c>
-      <c r="H28" s="88"/>
+      <c r="H28" s="95"/>
       <c r="I28" s="12" t="s">
         <v>139</v>
       </c>
@@ -4450,235 +4426,235 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1">
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>1</v>
       </c>
-      <c r="B29" s="97" t="s">
+      <c r="B29" s="96" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="98"/>
-      <c r="D29" s="98"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
-      <c r="G29" s="97" t="s">
+      <c r="C29" s="97"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="97"/>
+      <c r="G29" s="96" t="s">
         <v>249</v>
       </c>
-      <c r="H29" s="98"/>
-      <c r="I29" s="98"/>
-      <c r="J29" s="98"/>
-    </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1">
+      <c r="H29" s="97"/>
+      <c r="I29" s="97"/>
+      <c r="J29" s="97"/>
+    </row>
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>2</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="C30" s="62"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="62"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="61" t="s">
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="H30" s="62"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-    </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1">
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+    </row>
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>3</v>
       </c>
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="56" t="s">
         <v>260</v>
       </c>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
-    </row>
-    <row r="32" spans="1:10" ht="18" customHeight="1">
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+    </row>
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>4</v>
       </c>
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="56" t="s">
         <v>141</v>
       </c>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="61" t="s">
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-    </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1">
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+    </row>
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>5</v>
       </c>
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="56" t="s">
         <v>227</v>
       </c>
-      <c r="C33" s="62"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="61" t="s">
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="56" t="s">
         <v>264</v>
       </c>
-      <c r="H33" s="62"/>
-      <c r="I33" s="62"/>
-      <c r="J33" s="62"/>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1">
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+    </row>
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>6</v>
       </c>
-      <c r="B34" s="61" t="s">
+      <c r="B34" s="56" t="s">
         <v>268</v>
       </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="61" t="s">
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="56" t="s">
         <v>269</v>
       </c>
-      <c r="H34" s="62"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="62"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
         <v>7</v>
       </c>
-      <c r="B35" s="106" t="s">
+      <c r="B35" s="83" t="s">
         <v>273</v>
       </c>
       <c r="C35" s="84"/>
       <c r="D35" s="84"/>
       <c r="E35" s="84"/>
       <c r="F35" s="84"/>
-      <c r="G35" s="106" t="s">
+      <c r="G35" s="83" t="s">
         <v>274</v>
       </c>
       <c r="H35" s="84"/>
       <c r="I35" s="84"/>
       <c r="J35" s="84"/>
     </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1"/>
-    <row r="37" spans="1:10" ht="18" customHeight="1"/>
-    <row r="38" spans="1:10" ht="18" customHeight="1"/>
-    <row r="39" spans="1:10" ht="18" customHeight="1"/>
-    <row r="40" spans="1:10" ht="18" customHeight="1"/>
-    <row r="41" spans="1:10" ht="18" customHeight="1"/>
-    <row r="42" spans="1:10" ht="18" customHeight="1"/>
-    <row r="43" spans="1:10" ht="18" customHeight="1"/>
-    <row r="44" spans="1:10" ht="18" customHeight="1"/>
-    <row r="45" spans="1:10" ht="18" customHeight="1"/>
-    <row r="46" spans="1:10" ht="18" customHeight="1"/>
-    <row r="47" spans="1:10" ht="18" customHeight="1"/>
-    <row r="48" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A48" s="66" t="s">
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="64"/>
-      <c r="C48" s="63" t="s">
+      <c r="B48" s="54"/>
+      <c r="C48" s="68" t="s">
         <v>598</v>
       </c>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="64"/>
-      <c r="I48" s="64"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
       <c r="J48" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+    <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="B49" s="64"/>
-      <c r="C49" s="64"/>
-      <c r="D49" s="64"/>
-      <c r="E49" s="64"/>
-      <c r="F49" s="64"/>
-      <c r="G49" s="64"/>
-      <c r="H49" s="64"/>
-      <c r="I49" s="64"/>
-      <c r="J49" s="64"/>
-    </row>
-    <row r="50" spans="1:10" ht="11.25" customHeight="1">
-      <c r="A50" s="111" t="s">
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+    </row>
+    <row r="50" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="86" t="s">
         <v>276</v>
       </c>
-      <c r="B50" s="112"/>
-      <c r="C50" s="112"/>
-      <c r="D50" s="112"/>
-      <c r="E50" s="112"/>
-      <c r="F50" s="112"/>
-      <c r="G50" s="112"/>
-      <c r="H50" s="112"/>
-      <c r="I50" s="112"/>
-      <c r="J50" s="112"/>
-    </row>
-    <row r="51" spans="1:10" s="40" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A51" s="82" t="s">
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+    </row>
+    <row r="51" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="111" t="s">
         <v>277</v>
       </c>
-      <c r="B51" s="82"/>
-      <c r="C51" s="82"/>
-      <c r="D51" s="82"/>
-      <c r="E51" s="82"/>
-      <c r="F51" s="82"/>
-      <c r="G51" s="82"/>
-      <c r="H51" s="82"/>
-      <c r="I51" s="82"/>
-      <c r="J51" s="82"/>
-    </row>
-    <row r="52" spans="1:10" ht="12" customHeight="1">
-      <c r="A52" s="92" t="s">
+      <c r="B51" s="111"/>
+      <c r="C51" s="111"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="111"/>
+      <c r="F51" s="111"/>
+      <c r="G51" s="111"/>
+      <c r="H51" s="111"/>
+      <c r="I51" s="111"/>
+      <c r="J51" s="111"/>
+    </row>
+    <row r="52" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="B52" s="64"/>
-      <c r="C52" s="64"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="64"/>
-      <c r="F52" s="64"/>
-      <c r="G52" s="64"/>
-      <c r="H52" s="64"/>
-      <c r="I52" s="91" t="s">
+      <c r="B52" s="54"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="54"/>
+      <c r="I52" s="55" t="s">
         <v>185</v>
       </c>
-      <c r="J52" s="64"/>
-    </row>
-    <row r="53" spans="1:10" ht="12" customHeight="1" thickBot="1">
-      <c r="A53" s="92" t="s">
+      <c r="J52" s="54"/>
+    </row>
+    <row r="53" spans="1:10" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="64"/>
-      <c r="C53" s="64"/>
-      <c r="D53" s="64"/>
-      <c r="E53" s="64"/>
-      <c r="F53" s="64"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="64"/>
-      <c r="I53" s="91" t="s">
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="54"/>
+      <c r="I53" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="J53" s="64"/>
-    </row>
-    <row r="54" spans="1:10" ht="10.5" customHeight="1">
+      <c r="J53" s="54"/>
+    </row>
+    <row r="54" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>4</v>
       </c>
@@ -4697,10 +4673,10 @@
       <c r="F54" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="75" t="s">
+      <c r="G54" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H54" s="75"/>
+      <c r="H54" s="85"/>
       <c r="I54" s="2" t="s">
         <v>11</v>
       </c>
@@ -4708,7 +4684,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="10.5" customHeight="1">
+    <row r="55" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>280</v>
       </c>
@@ -4727,10 +4703,10 @@
       <c r="F55" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G55" s="76" t="s">
+      <c r="G55" s="92" t="s">
         <v>194</v>
       </c>
-      <c r="H55" s="77"/>
+      <c r="H55" s="93"/>
       <c r="I55" s="7" t="s">
         <v>49</v>
       </c>
@@ -4738,7 +4714,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="10.5" customHeight="1">
+    <row r="56" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>281</v>
       </c>
@@ -4748,27 +4724,27 @@
       <c r="C56" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D56" s="39" t="s">
+      <c r="D56" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E56" s="46" t="s">
+      <c r="E56" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="F56" s="39" t="s">
+      <c r="F56" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G56" s="76" t="s">
+      <c r="G56" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="H56" s="77"/>
-      <c r="I56" s="38" t="s">
+      <c r="H56" s="93"/>
+      <c r="I56" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J56" s="38" t="s">
+      <c r="J56" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="10.5" customHeight="1">
+    <row r="57" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>279</v>
       </c>
@@ -4787,10 +4763,10 @@
       <c r="F57" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G57" s="76" t="s">
+      <c r="G57" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="H57" s="77"/>
+      <c r="H57" s="93"/>
       <c r="I57" s="7" t="s">
         <v>44</v>
       </c>
@@ -4798,7 +4774,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="10.5" customHeight="1">
+    <row r="58" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>288</v>
       </c>
@@ -4817,10 +4793,10 @@
       <c r="F58" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G58" s="76" t="s">
+      <c r="G58" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="H58" s="77"/>
+      <c r="H58" s="93"/>
       <c r="I58" s="7" t="s">
         <v>22</v>
       </c>
@@ -4828,7 +4804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="10.5" customHeight="1">
+    <row r="59" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>290</v>
       </c>
@@ -4847,10 +4823,10 @@
       <c r="F59" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="G59" s="76" t="s">
+      <c r="G59" s="92" t="s">
         <v>207</v>
       </c>
-      <c r="H59" s="77"/>
+      <c r="H59" s="93"/>
       <c r="I59" s="7" t="s">
         <v>18</v>
       </c>
@@ -4858,7 +4834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="10.5" customHeight="1">
+    <row r="60" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>278</v>
       </c>
@@ -4877,10 +4853,10 @@
       <c r="F60" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G60" s="76" t="s">
+      <c r="G60" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="H60" s="77"/>
+      <c r="H60" s="93"/>
       <c r="I60" s="7" t="s">
         <v>40</v>
       </c>
@@ -4888,7 +4864,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="10.5" customHeight="1">
+    <row r="61" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>195</v>
       </c>
@@ -4898,57 +4874,57 @@
       <c r="C61" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D61" s="39" t="s">
+      <c r="D61" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E61" s="46" t="s">
+      <c r="E61" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="F61" s="39" t="s">
+      <c r="F61" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G61" s="76" t="s">
+      <c r="G61" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="H61" s="77"/>
-      <c r="I61" s="38" t="s">
+      <c r="H61" s="93"/>
+      <c r="I61" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J61" s="38" t="s">
+      <c r="J61" s="7" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="10.5" customHeight="1">
-      <c r="A62" s="48" t="s">
+    <row r="62" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="37" t="s">
         <v>292</v>
       </c>
-      <c r="B62" s="51">
+      <c r="B62" s="39">
         <v>8</v>
       </c>
-      <c r="C62" s="52" t="s">
+      <c r="C62" s="40" t="s">
         <v>103</v>
       </c>
       <c r="D62" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="E62" s="41" t="s">
+      <c r="E62" s="30" t="s">
         <v>200</v>
       </c>
       <c r="F62" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="G62" s="113" t="s">
+      <c r="G62" s="87" t="s">
         <v>205</v>
       </c>
-      <c r="H62" s="114"/>
-      <c r="I62" s="41" t="s">
+      <c r="H62" s="88"/>
+      <c r="I62" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="J62" s="41" t="s">
+      <c r="J62" s="30" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="10.5" customHeight="1" thickBot="1">
+    <row r="63" spans="1:10" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
         <v>282</v>
       </c>
@@ -4961,7 +4937,7 @@
       <c r="D63" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="47" t="s">
+      <c r="E63" s="32" t="s">
         <v>546</v>
       </c>
       <c r="F63" s="11" t="s">
@@ -4978,248 +4954,248 @@
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="9.75" customHeight="1">
+    <row r="64" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>1</v>
       </c>
-      <c r="B64" s="72" t="s">
+      <c r="B64" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="C64" s="73"/>
-      <c r="D64" s="73"/>
-      <c r="E64" s="73"/>
-      <c r="F64" s="74"/>
-      <c r="G64" s="72" t="s">
+      <c r="C64" s="113"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="114"/>
+      <c r="G64" s="112" t="s">
         <v>285</v>
       </c>
-      <c r="H64" s="78"/>
-      <c r="I64" s="78"/>
-      <c r="J64" s="79"/>
-    </row>
-    <row r="65" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H64" s="115"/>
+      <c r="I64" s="115"/>
+      <c r="J64" s="116"/>
+    </row>
+    <row r="65" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>2</v>
       </c>
-      <c r="B65" s="81" t="s">
+      <c r="B65" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="C65" s="68"/>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="69"/>
-      <c r="G65" s="81" t="s">
+      <c r="C65" s="62"/>
+      <c r="D65" s="62"/>
+      <c r="E65" s="62"/>
+      <c r="F65" s="63"/>
+      <c r="G65" s="89" t="s">
         <v>286</v>
       </c>
-      <c r="H65" s="68"/>
-      <c r="I65" s="68"/>
-      <c r="J65" s="69"/>
-    </row>
-    <row r="66" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H65" s="62"/>
+      <c r="I65" s="62"/>
+      <c r="J65" s="63"/>
+    </row>
+    <row r="66" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>3</v>
       </c>
-      <c r="B66" s="81" t="s">
+      <c r="B66" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="C66" s="68"/>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="81" t="s">
+      <c r="C66" s="62"/>
+      <c r="D66" s="62"/>
+      <c r="E66" s="62"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="89" t="s">
         <v>284</v>
       </c>
-      <c r="H66" s="68"/>
-      <c r="I66" s="68"/>
-      <c r="J66" s="69"/>
-    </row>
-    <row r="67" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H66" s="62"/>
+      <c r="I66" s="62"/>
+      <c r="J66" s="63"/>
+    </row>
+    <row r="67" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>4</v>
       </c>
-      <c r="B67" s="81" t="s">
+      <c r="B67" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="C67" s="68"/>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="69"/>
-      <c r="G67" s="81" t="s">
+      <c r="C67" s="62"/>
+      <c r="D67" s="62"/>
+      <c r="E67" s="62"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="89" t="s">
         <v>289</v>
       </c>
-      <c r="H67" s="68"/>
-      <c r="I67" s="68"/>
-      <c r="J67" s="69"/>
-    </row>
-    <row r="68" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H67" s="62"/>
+      <c r="I67" s="62"/>
+      <c r="J67" s="63"/>
+    </row>
+    <row r="68" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>5</v>
       </c>
-      <c r="B68" s="67" t="s">
+      <c r="B68" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="C68" s="68"/>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="69"/>
-      <c r="G68" s="67" t="s">
+      <c r="C68" s="62"/>
+      <c r="D68" s="62"/>
+      <c r="E68" s="62"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="61" t="s">
         <v>291</v>
       </c>
-      <c r="H68" s="68"/>
-      <c r="I68" s="68"/>
-      <c r="J68" s="69"/>
-    </row>
-    <row r="69" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H68" s="62"/>
+      <c r="I68" s="62"/>
+      <c r="J68" s="63"/>
+    </row>
+    <row r="69" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>6</v>
       </c>
-      <c r="B69" s="81" t="s">
+      <c r="B69" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="C69" s="68"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="69"/>
-      <c r="G69" s="81" t="s">
+      <c r="C69" s="62"/>
+      <c r="D69" s="62"/>
+      <c r="E69" s="62"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="89" t="s">
         <v>283</v>
       </c>
-      <c r="H69" s="68"/>
-      <c r="I69" s="68"/>
-      <c r="J69" s="69"/>
-    </row>
-    <row r="70" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H69" s="62"/>
+      <c r="I69" s="62"/>
+      <c r="J69" s="63"/>
+    </row>
+    <row r="70" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>7</v>
       </c>
-      <c r="B70" s="81" t="s">
+      <c r="B70" s="89" t="s">
         <v>197</v>
       </c>
-      <c r="C70" s="68"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="68"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="81" t="s">
+      <c r="C70" s="62"/>
+      <c r="D70" s="62"/>
+      <c r="E70" s="62"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="89" t="s">
         <v>196</v>
       </c>
-      <c r="H70" s="68"/>
-      <c r="I70" s="68"/>
-      <c r="J70" s="69"/>
-    </row>
-    <row r="71" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H70" s="62"/>
+      <c r="I70" s="62"/>
+      <c r="J70" s="63"/>
+    </row>
+    <row r="71" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>8</v>
       </c>
-      <c r="B71" s="67" t="s">
+      <c r="B71" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="C71" s="68"/>
-      <c r="D71" s="68"/>
-      <c r="E71" s="68"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="67" t="s">
+      <c r="C71" s="62"/>
+      <c r="D71" s="62"/>
+      <c r="E71" s="62"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="61" t="s">
         <v>293</v>
       </c>
-      <c r="H71" s="68"/>
-      <c r="I71" s="68"/>
-      <c r="J71" s="69"/>
-    </row>
-    <row r="72" spans="1:10" ht="9.75" customHeight="1" thickBot="1">
+      <c r="H71" s="62"/>
+      <c r="I71" s="62"/>
+      <c r="J71" s="63"/>
+    </row>
+    <row r="72" spans="1:10" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>9</v>
       </c>
-      <c r="B72" s="93" t="s">
+      <c r="B72" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="C72" s="94"/>
-      <c r="D72" s="94"/>
-      <c r="E72" s="94"/>
-      <c r="F72" s="95"/>
-      <c r="G72" s="93" t="s">
+      <c r="C72" s="102"/>
+      <c r="D72" s="102"/>
+      <c r="E72" s="102"/>
+      <c r="F72" s="103"/>
+      <c r="G72" s="101" t="s">
         <v>287</v>
       </c>
-      <c r="H72" s="94"/>
-      <c r="I72" s="94"/>
-      <c r="J72" s="95"/>
-    </row>
-    <row r="73" spans="1:10" ht="3" customHeight="1"/>
-    <row r="74" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A74" s="66" t="s">
+      <c r="H72" s="102"/>
+      <c r="I72" s="102"/>
+      <c r="J72" s="103"/>
+    </row>
+    <row r="73" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="B74" s="64"/>
-      <c r="C74" s="63" t="s">
+      <c r="B74" s="54"/>
+      <c r="C74" s="68" t="s">
         <v>599</v>
       </c>
-      <c r="D74" s="64"/>
-      <c r="E74" s="64"/>
-      <c r="F74" s="64"/>
-      <c r="G74" s="64"/>
-      <c r="H74" s="64"/>
-      <c r="I74" s="64"/>
-      <c r="J74" s="53" t="s">
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="54"/>
+      <c r="I74" s="54"/>
+      <c r="J74" s="41" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="13.5" customHeight="1">
+    <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B75" s="64"/>
-      <c r="C75" s="64"/>
-      <c r="D75" s="64"/>
-      <c r="E75" s="64"/>
-      <c r="F75" s="64"/>
-      <c r="G75" s="64"/>
-      <c r="H75" s="64"/>
-      <c r="I75" s="64"/>
-      <c r="J75" s="64"/>
-    </row>
-    <row r="76" spans="1:10" ht="12" customHeight="1">
-      <c r="A76" s="96" t="s">
+      <c r="B75" s="54"/>
+      <c r="C75" s="54"/>
+      <c r="D75" s="54"/>
+      <c r="E75" s="54"/>
+      <c r="F75" s="54"/>
+      <c r="G75" s="54"/>
+      <c r="H75" s="54"/>
+      <c r="I75" s="54"/>
+      <c r="J75" s="54"/>
+    </row>
+    <row r="76" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="53" t="s">
         <v>295</v>
       </c>
-      <c r="B76" s="64"/>
-      <c r="C76" s="64"/>
-      <c r="D76" s="64"/>
-      <c r="E76" s="64"/>
-      <c r="F76" s="64"/>
-      <c r="G76" s="64"/>
-      <c r="H76" s="64"/>
-      <c r="I76" s="64"/>
-      <c r="J76" s="64"/>
-    </row>
-    <row r="77" spans="1:10" ht="12" customHeight="1">
-      <c r="A77" s="102" t="s">
+      <c r="B76" s="54"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="54"/>
+      <c r="H76" s="54"/>
+      <c r="I76" s="54"/>
+      <c r="J76" s="54"/>
+    </row>
+    <row r="77" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="60" t="s">
         <v>296</v>
       </c>
-      <c r="B77" s="64"/>
-      <c r="C77" s="64"/>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="64"/>
-      <c r="H77" s="64"/>
-      <c r="I77" s="89" t="s">
+      <c r="B77" s="54"/>
+      <c r="C77" s="54"/>
+      <c r="D77" s="54"/>
+      <c r="E77" s="54"/>
+      <c r="F77" s="54"/>
+      <c r="G77" s="54"/>
+      <c r="H77" s="54"/>
+      <c r="I77" s="91" t="s">
         <v>184</v>
       </c>
-      <c r="J77" s="64"/>
-    </row>
-    <row r="78" spans="1:10" ht="12" customHeight="1" thickBot="1">
-      <c r="A78" s="102" t="s">
+      <c r="J77" s="54"/>
+    </row>
+    <row r="78" spans="1:10" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="B78" s="64"/>
-      <c r="C78" s="64"/>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="64"/>
-      <c r="H78" s="64"/>
-      <c r="I78" s="89" t="s">
+      <c r="B78" s="54"/>
+      <c r="C78" s="54"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="54"/>
+      <c r="G78" s="54"/>
+      <c r="H78" s="54"/>
+      <c r="I78" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="J78" s="64"/>
-    </row>
-    <row r="79" spans="1:10" ht="10.5" customHeight="1">
+      <c r="J78" s="54"/>
+    </row>
+    <row r="79" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>4</v>
       </c>
@@ -5238,10 +5214,10 @@
       <c r="F79" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G79" s="75" t="s">
+      <c r="G79" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H79" s="75"/>
+      <c r="H79" s="85"/>
       <c r="I79" s="2" t="s">
         <v>11</v>
       </c>
@@ -5249,8 +5225,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="10.5" customHeight="1">
-      <c r="A80" s="48" t="s">
+    <row r="80" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="37" t="s">
         <v>299</v>
       </c>
       <c r="B80" s="4">
@@ -5262,25 +5238,25 @@
       <c r="D80" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E80" s="41" t="s">
+      <c r="E80" s="30" t="s">
         <v>198</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G80" s="70" t="s">
+      <c r="G80" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="H80" s="71"/>
-      <c r="I80" s="41" t="s">
+      <c r="H80" s="59"/>
+      <c r="I80" s="30" t="s">
         <v>166</v>
       </c>
       <c r="J80" s="7" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="10.5" customHeight="1">
-      <c r="A81" s="48" t="s">
+    <row r="81" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="37" t="s">
         <v>304</v>
       </c>
       <c r="B81" s="4">
@@ -5292,16 +5268,16 @@
       <c r="D81" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="41" t="s">
+      <c r="E81" s="30" t="s">
         <v>204</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G81" s="70" t="s">
+      <c r="G81" s="58" t="s">
         <v>303</v>
       </c>
-      <c r="H81" s="71"/>
+      <c r="H81" s="59"/>
       <c r="I81" s="7" t="s">
         <v>166</v>
       </c>
@@ -5309,8 +5285,8 @@
         <v>167</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="10.5" customHeight="1">
-      <c r="A82" s="48" t="s">
+    <row r="82" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="37" t="s">
         <v>307</v>
       </c>
       <c r="B82" s="4">
@@ -5322,16 +5298,16 @@
       <c r="D82" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E82" s="46" t="s">
+      <c r="E82" s="30" t="s">
         <v>200</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G82" s="70" t="s">
+      <c r="G82" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="H82" s="71"/>
+      <c r="H82" s="59"/>
       <c r="I82" s="7" t="s">
         <v>89</v>
       </c>
@@ -5339,8 +5315,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="10.5" customHeight="1">
-      <c r="A83" s="48" t="s">
+    <row r="83" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="37" t="s">
         <v>311</v>
       </c>
       <c r="B83" s="4">
@@ -5358,10 +5334,10 @@
       <c r="F83" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G83" s="70" t="s">
+      <c r="G83" s="58" t="s">
         <v>310</v>
       </c>
-      <c r="H83" s="71"/>
+      <c r="H83" s="59"/>
       <c r="I83" s="7" t="s">
         <v>166</v>
       </c>
@@ -5369,8 +5345,8 @@
         <v>167</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="10.5" customHeight="1">
-      <c r="A84" s="48" t="s">
+    <row r="84" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="37" t="s">
         <v>317</v>
       </c>
       <c r="B84" s="4">
@@ -5382,16 +5358,16 @@
       <c r="D84" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E84" s="46" t="s">
+      <c r="E84" s="30" t="s">
         <v>228</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G84" s="70" t="s">
+      <c r="G84" s="58" t="s">
         <v>316</v>
       </c>
-      <c r="H84" s="71"/>
+      <c r="H84" s="59"/>
       <c r="I84" s="7" t="s">
         <v>139</v>
       </c>
@@ -5399,8 +5375,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A85" s="54" t="s">
+    <row r="85" spans="1:10" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="42" t="s">
         <v>320</v>
       </c>
       <c r="B85" s="9">
@@ -5412,16 +5388,16 @@
       <c r="D85" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E85" s="42" t="s">
+      <c r="E85" s="32" t="s">
         <v>235</v>
       </c>
       <c r="F85" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="G85" s="83" t="s">
+      <c r="G85" s="90" t="s">
         <v>155</v>
       </c>
-      <c r="H85" s="108"/>
+      <c r="H85" s="98"/>
       <c r="I85" s="12" t="s">
         <v>88</v>
       </c>
@@ -5429,187 +5405,180 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="9.75" customHeight="1">
+    <row r="86" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>1</v>
       </c>
-      <c r="B86" s="80" t="s">
+      <c r="B86" s="66" t="s">
         <v>300</v>
       </c>
-      <c r="C86" s="62"/>
-      <c r="D86" s="62"/>
-      <c r="E86" s="62"/>
-      <c r="F86" s="62"/>
-      <c r="G86" s="80" t="s">
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="H86" s="62"/>
-      <c r="I86" s="62"/>
-      <c r="J86" s="62"/>
-    </row>
-    <row r="87" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="57"/>
+    </row>
+    <row r="87" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>2</v>
       </c>
-      <c r="B87" s="80" t="s">
+      <c r="B87" s="66" t="s">
         <v>305</v>
       </c>
-      <c r="C87" s="62"/>
-      <c r="D87" s="62"/>
-      <c r="E87" s="62"/>
-      <c r="F87" s="62"/>
-      <c r="G87" s="80" t="s">
+      <c r="C87" s="57"/>
+      <c r="D87" s="57"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="57"/>
+      <c r="G87" s="66" t="s">
         <v>306</v>
       </c>
-      <c r="H87" s="62"/>
-      <c r="I87" s="62"/>
-      <c r="J87" s="62"/>
-    </row>
-    <row r="88" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H87" s="57"/>
+      <c r="I87" s="57"/>
+      <c r="J87" s="57"/>
+    </row>
+    <row r="88" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>3</v>
       </c>
-      <c r="B88" s="80" t="s">
+      <c r="B88" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="C88" s="62"/>
-      <c r="D88" s="62"/>
-      <c r="E88" s="62"/>
-      <c r="F88" s="62"/>
-      <c r="G88" s="80" t="s">
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="57"/>
+      <c r="G88" s="66" t="s">
         <v>308</v>
       </c>
-      <c r="H88" s="62"/>
-      <c r="I88" s="62"/>
-      <c r="J88" s="62"/>
-    </row>
-    <row r="89" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H88" s="57"/>
+      <c r="I88" s="57"/>
+      <c r="J88" s="57"/>
+    </row>
+    <row r="89" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>4</v>
       </c>
-      <c r="B89" s="80" t="s">
+      <c r="B89" s="66" t="s">
         <v>312</v>
       </c>
-      <c r="C89" s="62"/>
-      <c r="D89" s="62"/>
-      <c r="E89" s="62"/>
-      <c r="F89" s="62"/>
-      <c r="G89" s="80" t="s">
+      <c r="C89" s="57"/>
+      <c r="D89" s="57"/>
+      <c r="E89" s="57"/>
+      <c r="F89" s="57"/>
+      <c r="G89" s="66" t="s">
         <v>313</v>
       </c>
-      <c r="H89" s="62"/>
-      <c r="I89" s="62"/>
-      <c r="J89" s="62"/>
-    </row>
-    <row r="90" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H89" s="57"/>
+      <c r="I89" s="57"/>
+      <c r="J89" s="57"/>
+    </row>
+    <row r="90" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>5</v>
       </c>
-      <c r="B90" s="80" t="s">
+      <c r="B90" s="66" t="s">
         <v>318</v>
       </c>
-      <c r="C90" s="62"/>
-      <c r="D90" s="62"/>
-      <c r="E90" s="62"/>
-      <c r="F90" s="62"/>
-      <c r="G90" s="80" t="s">
+      <c r="C90" s="57"/>
+      <c r="D90" s="57"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="57"/>
+      <c r="G90" s="66" t="s">
         <v>319</v>
       </c>
-      <c r="H90" s="62"/>
-      <c r="I90" s="62"/>
-      <c r="J90" s="62"/>
-    </row>
-    <row r="91" spans="1:10" ht="9.75" customHeight="1" thickBot="1">
+      <c r="H90" s="57"/>
+      <c r="I90" s="57"/>
+      <c r="J90" s="57"/>
+    </row>
+    <row r="91" spans="1:10" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
         <v>6</v>
       </c>
-      <c r="B91" s="83" t="s">
+      <c r="B91" s="90" t="s">
         <v>157</v>
       </c>
       <c r="C91" s="84"/>
       <c r="D91" s="84"/>
       <c r="E91" s="84"/>
       <c r="F91" s="84"/>
-      <c r="G91" s="83" t="s">
+      <c r="G91" s="90" t="s">
         <v>321</v>
       </c>
       <c r="H91" s="84"/>
       <c r="I91" s="84"/>
       <c r="J91" s="84"/>
     </row>
-    <row r="92" spans="1:10" ht="3" customHeight="1"/>
-    <row r="93" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A93" s="66" t="s">
+    <row r="92" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="B93" s="64"/>
-      <c r="C93" s="63" t="s">
+      <c r="B93" s="54"/>
+      <c r="C93" s="68" t="s">
         <v>600</v>
       </c>
-      <c r="D93" s="64"/>
-      <c r="E93" s="64"/>
-      <c r="F93" s="64"/>
-      <c r="G93" s="64"/>
-      <c r="H93" s="64"/>
-      <c r="I93" s="64"/>
-      <c r="J93" s="53" t="s">
+      <c r="D93" s="54"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="54"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="54"/>
+      <c r="I93" s="54"/>
+      <c r="J93" s="41" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B94" s="64"/>
-      <c r="C94" s="64"/>
-      <c r="D94" s="64"/>
-      <c r="E94" s="64"/>
-      <c r="F94" s="64"/>
-      <c r="G94" s="64"/>
-      <c r="H94" s="64"/>
-      <c r="I94" s="64"/>
-      <c r="J94" s="64"/>
-    </row>
-    <row r="95" spans="1:10" ht="12" customHeight="1">
-      <c r="A95" s="96" t="s">
+      <c r="B94" s="54"/>
+      <c r="C94" s="54"/>
+      <c r="D94" s="54"/>
+      <c r="E94" s="54"/>
+      <c r="F94" s="54"/>
+      <c r="G94" s="54"/>
+      <c r="H94" s="54"/>
+      <c r="I94" s="54"/>
+      <c r="J94" s="54"/>
+    </row>
+    <row r="95" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="53" t="s">
         <v>322</v>
       </c>
-      <c r="B95" s="64"/>
-      <c r="C95" s="64"/>
-      <c r="D95" s="64"/>
-      <c r="E95" s="64"/>
-      <c r="F95" s="64"/>
-      <c r="G95" s="64"/>
-      <c r="H95" s="64"/>
-      <c r="I95" s="64"/>
-      <c r="J95" s="64"/>
-    </row>
-    <row r="96" spans="1:10" ht="12" customHeight="1">
-      <c r="A96" s="56" t="s">
+      <c r="B95" s="54"/>
+      <c r="C95" s="54"/>
+      <c r="D95" s="54"/>
+      <c r="E95" s="54"/>
+      <c r="F95" s="54"/>
+      <c r="G95" s="54"/>
+      <c r="H95" s="54"/>
+      <c r="I95" s="54"/>
+      <c r="J95" s="54"/>
+    </row>
+    <row r="96" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="50"/>
-      <c r="C96" s="50"/>
-      <c r="D96" s="50"/>
-      <c r="E96" s="50"/>
-      <c r="F96" s="50"/>
-      <c r="G96" s="50"/>
-      <c r="H96" s="50"/>
       <c r="I96" s="29"/>
     </row>
-    <row r="97" spans="1:10" ht="12" customHeight="1" thickBot="1">
-      <c r="A97" s="102" t="s">
+    <row r="97" spans="1:10" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="60" t="s">
         <v>323</v>
       </c>
-      <c r="B97" s="64"/>
-      <c r="C97" s="64"/>
-      <c r="D97" s="64"/>
-      <c r="E97" s="64"/>
-      <c r="F97" s="64"/>
-      <c r="G97" s="64"/>
-      <c r="H97" s="64"/>
-    </row>
-    <row r="98" spans="1:10" ht="10.5" customHeight="1">
+      <c r="B97" s="54"/>
+      <c r="C97" s="54"/>
+      <c r="D97" s="54"/>
+      <c r="E97" s="54"/>
+      <c r="F97" s="54"/>
+      <c r="G97" s="54"/>
+      <c r="H97" s="54"/>
+    </row>
+    <row r="98" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>4</v>
       </c>
@@ -5628,10 +5597,10 @@
       <c r="F98" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G98" s="75" t="s">
+      <c r="G98" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H98" s="75"/>
+      <c r="H98" s="85"/>
       <c r="I98" s="2" t="s">
         <v>11</v>
       </c>
@@ -5639,7 +5608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="10.5" customHeight="1">
+    <row r="99" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>328</v>
       </c>
@@ -5658,10 +5627,10 @@
       <c r="F99" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G99" s="70" t="s">
+      <c r="G99" s="58" t="s">
         <v>327</v>
       </c>
-      <c r="H99" s="71"/>
+      <c r="H99" s="59"/>
       <c r="I99" s="7" t="s">
         <v>165</v>
       </c>
@@ -5669,7 +5638,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="10.5" customHeight="1">
+    <row r="100" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>331</v>
       </c>
@@ -5688,10 +5657,10 @@
       <c r="F100" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="G100" s="70" t="s">
+      <c r="G100" s="58" t="s">
         <v>334</v>
       </c>
-      <c r="H100" s="71"/>
+      <c r="H100" s="59"/>
       <c r="I100" s="7" t="s">
         <v>25</v>
       </c>
@@ -5699,7 +5668,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="10.5" customHeight="1">
+    <row r="101" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>13</v>
       </c>
@@ -5709,25 +5678,25 @@
       <c r="C101" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D101" s="44" t="s">
+      <c r="D101" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E101" s="43"/>
-      <c r="F101" s="44" t="s">
+      <c r="E101" s="7"/>
+      <c r="F101" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G101" s="70" t="s">
+      <c r="G101" s="58" t="s">
         <v>338</v>
       </c>
-      <c r="H101" s="71"/>
-      <c r="I101" s="43" t="s">
+      <c r="H101" s="59"/>
+      <c r="I101" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="J101" s="43" t="s">
+      <c r="J101" s="7" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="10.5" customHeight="1">
+    <row r="102" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>344</v>
       </c>
@@ -5737,27 +5706,27 @@
       <c r="C102" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D102" s="44" t="s">
+      <c r="D102" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E102" s="43" t="s">
+      <c r="E102" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F102" s="44" t="s">
+      <c r="F102" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G102" s="70" t="s">
+      <c r="G102" s="58" t="s">
         <v>342</v>
       </c>
-      <c r="H102" s="71"/>
-      <c r="I102" s="43" t="s">
+      <c r="H102" s="59"/>
+      <c r="I102" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="J102" s="43" t="s">
+      <c r="J102" s="7" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="10.5" customHeight="1">
+    <row r="103" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>350</v>
       </c>
@@ -5767,27 +5736,27 @@
       <c r="C103" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D103" s="44" t="s">
+      <c r="D103" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E103" s="46" t="s">
+      <c r="E103" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="F103" s="44" t="s">
+      <c r="F103" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G103" s="70" t="s">
+      <c r="G103" s="58" t="s">
         <v>348</v>
       </c>
-      <c r="H103" s="71"/>
-      <c r="I103" s="43" t="s">
+      <c r="H103" s="59"/>
+      <c r="I103" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="J103" s="43" t="s">
+      <c r="J103" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="10.5" customHeight="1">
+    <row r="104" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>325</v>
       </c>
@@ -5806,10 +5775,10 @@
       <c r="F104" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G104" s="70" t="s">
+      <c r="G104" s="58" t="s">
         <v>354</v>
       </c>
-      <c r="H104" s="71"/>
+      <c r="H104" s="59"/>
       <c r="I104" s="7" t="s">
         <v>356</v>
       </c>
@@ -5817,37 +5786,37 @@
         <v>357</v>
       </c>
     </row>
-    <row r="105" spans="1:10" s="40" customFormat="1" ht="10.5" customHeight="1">
-      <c r="A105" s="48" t="s">
+    <row r="105" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="37" t="s">
         <v>363</v>
       </c>
-      <c r="B105" s="51">
+      <c r="B105" s="39">
         <v>7</v>
       </c>
-      <c r="C105" s="52" t="s">
+      <c r="C105" s="40" t="s">
         <v>361</v>
       </c>
       <c r="D105" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E105" s="57" t="s">
+      <c r="E105" s="45" t="s">
         <v>364</v>
       </c>
       <c r="F105" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="G105" s="85" t="s">
+      <c r="G105" s="81" t="s">
         <v>362</v>
       </c>
-      <c r="H105" s="86"/>
-      <c r="I105" s="46" t="s">
+      <c r="H105" s="82"/>
+      <c r="I105" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="J105" s="46" t="s">
+      <c r="J105" s="30" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="106" spans="1:10" s="40" customFormat="1" ht="10.5" customHeight="1">
+    <row r="106" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>13</v>
       </c>
@@ -5857,27 +5826,27 @@
       <c r="C106" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="D106" s="39" t="s">
+      <c r="D106" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E106" s="38" t="s">
+      <c r="E106" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="F106" s="39" t="s">
+      <c r="F106" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G106" s="70" t="s">
+      <c r="G106" s="58" t="s">
         <v>368</v>
       </c>
-      <c r="H106" s="71"/>
-      <c r="I106" s="38" t="s">
+      <c r="H106" s="59"/>
+      <c r="I106" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J106" s="38" t="s">
+      <c r="J106" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="107" spans="1:10" s="40" customFormat="1" ht="10.5" customHeight="1">
+    <row r="107" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>371</v>
       </c>
@@ -5887,27 +5856,27 @@
       <c r="C107" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="D107" s="39" t="s">
+      <c r="D107" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E107" s="46" t="s">
+      <c r="E107" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="F107" s="39" t="s">
+      <c r="F107" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="G107" s="70" t="s">
+      <c r="G107" s="58" t="s">
         <v>370</v>
       </c>
-      <c r="H107" s="71"/>
-      <c r="I107" s="38" t="s">
+      <c r="H107" s="59"/>
+      <c r="I107" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J107" s="38" t="s">
+      <c r="J107" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="108" spans="1:10" s="40" customFormat="1" ht="10.5" customHeight="1">
+    <row r="108" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>377</v>
       </c>
@@ -5917,27 +5886,27 @@
       <c r="C108" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="D108" s="44" t="s">
+      <c r="D108" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E108" s="46" t="s">
+      <c r="E108" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="F108" s="44" t="s">
+      <c r="F108" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G108" s="70" t="s">
+      <c r="G108" s="58" t="s">
         <v>375</v>
       </c>
-      <c r="H108" s="71"/>
-      <c r="I108" s="43" t="s">
+      <c r="H108" s="59"/>
+      <c r="I108" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="J108" s="43" t="s">
+      <c r="J108" s="7" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="109" spans="1:10" s="40" customFormat="1" ht="10.5" customHeight="1">
+    <row r="109" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>384</v>
       </c>
@@ -5947,27 +5916,27 @@
       <c r="C109" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="D109" s="44" t="s">
+      <c r="D109" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E109" s="43" t="s">
+      <c r="E109" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F109" s="44" t="s">
+      <c r="F109" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G109" s="70" t="s">
+      <c r="G109" s="58" t="s">
         <v>381</v>
       </c>
-      <c r="H109" s="71"/>
-      <c r="I109" s="43" t="s">
+      <c r="H109" s="59"/>
+      <c r="I109" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="J109" s="43" t="s">
+      <c r="J109" s="7" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="110" spans="1:10" s="40" customFormat="1" ht="10.5" customHeight="1">
+    <row r="110" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>388</v>
       </c>
@@ -5977,27 +5946,27 @@
       <c r="C110" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D110" s="44" t="s">
+      <c r="D110" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E110" s="43" t="s">
+      <c r="E110" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="F110" s="44" t="s">
+      <c r="F110" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G110" s="70" t="s">
+      <c r="G110" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="H110" s="71"/>
-      <c r="I110" s="43" t="s">
+      <c r="H110" s="59"/>
+      <c r="I110" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="J110" s="43" t="s">
+      <c r="J110" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="10.5" customHeight="1" thickBot="1">
+    <row r="111" spans="1:10" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="8" t="s">
         <v>13</v>
       </c>
@@ -6016,10 +5985,10 @@
       <c r="F111" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G111" s="107" t="s">
+      <c r="G111" s="94" t="s">
         <v>392</v>
       </c>
-      <c r="H111" s="88"/>
+      <c r="H111" s="95"/>
       <c r="I111" s="12" t="s">
         <v>608</v>
       </c>
@@ -6027,314 +5996,314 @@
         <v>62</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="9.75" customHeight="1">
+    <row r="112" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>1</v>
       </c>
-      <c r="B112" s="61" t="s">
+      <c r="B112" s="56" t="s">
         <v>329</v>
       </c>
-      <c r="C112" s="62"/>
-      <c r="D112" s="62"/>
-      <c r="E112" s="62"/>
-      <c r="F112" s="62"/>
-      <c r="G112" s="61" t="s">
+      <c r="C112" s="57"/>
+      <c r="D112" s="57"/>
+      <c r="E112" s="57"/>
+      <c r="F112" s="57"/>
+      <c r="G112" s="56" t="s">
         <v>330</v>
       </c>
-      <c r="H112" s="62"/>
-      <c r="I112" s="62"/>
-      <c r="J112" s="62"/>
-    </row>
-    <row r="113" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H112" s="57"/>
+      <c r="I112" s="57"/>
+      <c r="J112" s="57"/>
+    </row>
+    <row r="113" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>2</v>
       </c>
-      <c r="B113" s="61" t="s">
+      <c r="B113" s="56" t="s">
         <v>335</v>
       </c>
-      <c r="C113" s="62"/>
-      <c r="D113" s="62"/>
-      <c r="E113" s="62"/>
-      <c r="F113" s="62"/>
-      <c r="G113" s="61" t="s">
+      <c r="C113" s="57"/>
+      <c r="D113" s="57"/>
+      <c r="E113" s="57"/>
+      <c r="F113" s="57"/>
+      <c r="G113" s="56" t="s">
         <v>336</v>
       </c>
-      <c r="H113" s="62"/>
-      <c r="I113" s="62"/>
-      <c r="J113" s="62"/>
-    </row>
-    <row r="114" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H113" s="57"/>
+      <c r="I113" s="57"/>
+      <c r="J113" s="57"/>
+    </row>
+    <row r="114" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>3</v>
       </c>
-      <c r="B114" s="61" t="s">
+      <c r="B114" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C114" s="62"/>
-      <c r="D114" s="62"/>
-      <c r="E114" s="62"/>
-      <c r="F114" s="62"/>
-      <c r="G114" s="61"/>
-      <c r="H114" s="62"/>
-      <c r="I114" s="62"/>
-      <c r="J114" s="62"/>
-    </row>
-    <row r="115" spans="1:10" ht="9.75" customHeight="1">
+      <c r="C114" s="57"/>
+      <c r="D114" s="57"/>
+      <c r="E114" s="57"/>
+      <c r="F114" s="57"/>
+      <c r="G114" s="56"/>
+      <c r="H114" s="57"/>
+      <c r="I114" s="57"/>
+      <c r="J114" s="57"/>
+    </row>
+    <row r="115" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>4</v>
       </c>
-      <c r="B115" s="61" t="s">
+      <c r="B115" s="56" t="s">
         <v>345</v>
       </c>
-      <c r="C115" s="62"/>
-      <c r="D115" s="62"/>
-      <c r="E115" s="62"/>
-      <c r="F115" s="62"/>
-      <c r="G115" s="61" t="s">
+      <c r="C115" s="57"/>
+      <c r="D115" s="57"/>
+      <c r="E115" s="57"/>
+      <c r="F115" s="57"/>
+      <c r="G115" s="56" t="s">
         <v>346</v>
       </c>
-      <c r="H115" s="62"/>
-      <c r="I115" s="62"/>
-      <c r="J115" s="62"/>
-    </row>
-    <row r="116" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H115" s="57"/>
+      <c r="I115" s="57"/>
+      <c r="J115" s="57"/>
+    </row>
+    <row r="116" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>5</v>
       </c>
-      <c r="B116" s="61" t="s">
+      <c r="B116" s="56" t="s">
         <v>351</v>
       </c>
-      <c r="C116" s="62"/>
-      <c r="D116" s="62"/>
-      <c r="E116" s="62"/>
-      <c r="F116" s="62"/>
-      <c r="G116" s="61" t="s">
+      <c r="C116" s="57"/>
+      <c r="D116" s="57"/>
+      <c r="E116" s="57"/>
+      <c r="F116" s="57"/>
+      <c r="G116" s="56" t="s">
         <v>352</v>
       </c>
-      <c r="H116" s="62"/>
-      <c r="I116" s="62"/>
-      <c r="J116" s="62"/>
-    </row>
-    <row r="117" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H116" s="57"/>
+      <c r="I116" s="57"/>
+      <c r="J116" s="57"/>
+    </row>
+    <row r="117" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>6</v>
       </c>
-      <c r="B117" s="61" t="s">
+      <c r="B117" s="56" t="s">
         <v>358</v>
       </c>
-      <c r="C117" s="62"/>
-      <c r="D117" s="62"/>
-      <c r="E117" s="62"/>
-      <c r="F117" s="62"/>
-      <c r="G117" s="61" t="s">
+      <c r="C117" s="57"/>
+      <c r="D117" s="57"/>
+      <c r="E117" s="57"/>
+      <c r="F117" s="57"/>
+      <c r="G117" s="56" t="s">
         <v>359</v>
       </c>
-      <c r="H117" s="62"/>
-      <c r="I117" s="62"/>
-      <c r="J117" s="62"/>
-    </row>
-    <row r="118" spans="1:10" s="40" customFormat="1" ht="9.75" customHeight="1">
-      <c r="A118" s="55">
+      <c r="H117" s="57"/>
+      <c r="I117" s="57"/>
+      <c r="J117" s="57"/>
+    </row>
+    <row r="118" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="43">
         <v>7</v>
       </c>
-      <c r="B118" s="61" t="s">
+      <c r="B118" s="56" t="s">
         <v>365</v>
       </c>
-      <c r="C118" s="62"/>
-      <c r="D118" s="62"/>
-      <c r="E118" s="62"/>
-      <c r="F118" s="62"/>
-      <c r="G118" s="80" t="s">
+      <c r="C118" s="57"/>
+      <c r="D118" s="57"/>
+      <c r="E118" s="57"/>
+      <c r="F118" s="57"/>
+      <c r="G118" s="66" t="s">
         <v>366</v>
       </c>
-      <c r="H118" s="62"/>
-      <c r="I118" s="62"/>
-      <c r="J118" s="62"/>
-    </row>
-    <row r="119" spans="1:10" s="40" customFormat="1" ht="9.75" customHeight="1">
-      <c r="A119" s="55">
+      <c r="H118" s="57"/>
+      <c r="I118" s="57"/>
+      <c r="J118" s="57"/>
+    </row>
+    <row r="119" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="43">
         <v>8</v>
       </c>
-      <c r="B119" s="61" t="s">
+      <c r="B119" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C119" s="62"/>
-      <c r="D119" s="62"/>
-      <c r="E119" s="62"/>
-      <c r="F119" s="62"/>
-      <c r="G119" s="61"/>
-      <c r="H119" s="62"/>
-      <c r="I119" s="62"/>
-      <c r="J119" s="62"/>
-    </row>
-    <row r="120" spans="1:10" s="40" customFormat="1" ht="9.75" customHeight="1">
-      <c r="A120" s="55">
+      <c r="C119" s="57"/>
+      <c r="D119" s="57"/>
+      <c r="E119" s="57"/>
+      <c r="F119" s="57"/>
+      <c r="G119" s="56"/>
+      <c r="H119" s="57"/>
+      <c r="I119" s="57"/>
+      <c r="J119" s="57"/>
+    </row>
+    <row r="120" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="43">
         <v>9</v>
       </c>
-      <c r="B120" s="61" t="s">
+      <c r="B120" s="56" t="s">
         <v>372</v>
       </c>
-      <c r="C120" s="62"/>
-      <c r="D120" s="62"/>
-      <c r="E120" s="62"/>
-      <c r="F120" s="62"/>
-      <c r="G120" s="61" t="s">
+      <c r="C120" s="57"/>
+      <c r="D120" s="57"/>
+      <c r="E120" s="57"/>
+      <c r="F120" s="57"/>
+      <c r="G120" s="56" t="s">
         <v>373</v>
       </c>
-      <c r="H120" s="62"/>
-      <c r="I120" s="62"/>
-      <c r="J120" s="62"/>
-    </row>
-    <row r="121" spans="1:10" s="40" customFormat="1" ht="9.75" customHeight="1">
-      <c r="A121" s="55">
+      <c r="H120" s="57"/>
+      <c r="I120" s="57"/>
+      <c r="J120" s="57"/>
+    </row>
+    <row r="121" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="43">
         <v>10</v>
       </c>
-      <c r="B121" s="61" t="s">
+      <c r="B121" s="56" t="s">
         <v>378</v>
       </c>
-      <c r="C121" s="62"/>
-      <c r="D121" s="62"/>
-      <c r="E121" s="62"/>
-      <c r="F121" s="62"/>
-      <c r="G121" s="61" t="s">
+      <c r="C121" s="57"/>
+      <c r="D121" s="57"/>
+      <c r="E121" s="57"/>
+      <c r="F121" s="57"/>
+      <c r="G121" s="56" t="s">
         <v>379</v>
       </c>
-      <c r="H121" s="62"/>
-      <c r="I121" s="62"/>
-      <c r="J121" s="62"/>
-    </row>
-    <row r="122" spans="1:10" s="40" customFormat="1" ht="9.75" customHeight="1">
-      <c r="A122" s="55">
+      <c r="H121" s="57"/>
+      <c r="I121" s="57"/>
+      <c r="J121" s="57"/>
+    </row>
+    <row r="122" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="43">
         <v>11</v>
       </c>
-      <c r="B122" s="61" t="s">
+      <c r="B122" s="56" t="s">
         <v>386</v>
       </c>
-      <c r="C122" s="62"/>
-      <c r="D122" s="62"/>
-      <c r="E122" s="62"/>
-      <c r="F122" s="62"/>
-      <c r="G122" s="61" t="s">
+      <c r="C122" s="57"/>
+      <c r="D122" s="57"/>
+      <c r="E122" s="57"/>
+      <c r="F122" s="57"/>
+      <c r="G122" s="56" t="s">
         <v>387</v>
       </c>
-      <c r="H122" s="62"/>
-      <c r="I122" s="62"/>
-      <c r="J122" s="62"/>
-    </row>
-    <row r="123" spans="1:10" s="40" customFormat="1" ht="9.75" customHeight="1">
-      <c r="A123" s="55">
+      <c r="H122" s="57"/>
+      <c r="I122" s="57"/>
+      <c r="J122" s="57"/>
+    </row>
+    <row r="123" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="43">
         <v>12</v>
       </c>
-      <c r="B123" s="61" t="s">
+      <c r="B123" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="C123" s="62"/>
-      <c r="D123" s="62"/>
-      <c r="E123" s="62"/>
-      <c r="F123" s="62"/>
-      <c r="G123" s="61" t="s">
+      <c r="C123" s="57"/>
+      <c r="D123" s="57"/>
+      <c r="E123" s="57"/>
+      <c r="F123" s="57"/>
+      <c r="G123" s="56" t="s">
         <v>389</v>
       </c>
-      <c r="H123" s="62"/>
-      <c r="I123" s="62"/>
-      <c r="J123" s="62"/>
-    </row>
-    <row r="124" spans="1:10" ht="9.75" customHeight="1" thickBot="1">
+      <c r="H123" s="57"/>
+      <c r="I123" s="57"/>
+      <c r="J123" s="57"/>
+    </row>
+    <row r="124" spans="1:10" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="9">
         <v>13</v>
       </c>
-      <c r="B124" s="106" t="s">
+      <c r="B124" s="83" t="s">
         <v>27</v>
       </c>
       <c r="C124" s="84"/>
       <c r="D124" s="84"/>
       <c r="E124" s="84"/>
       <c r="F124" s="84"/>
-      <c r="G124" s="106"/>
+      <c r="G124" s="83"/>
       <c r="H124" s="84"/>
       <c r="I124" s="84"/>
       <c r="J124" s="84"/>
     </row>
-    <row r="125" spans="1:10" ht="6" customHeight="1"/>
-    <row r="126" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A126" s="66" t="s">
+    <row r="125" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="B126" s="64"/>
-      <c r="C126" s="63" t="s">
+      <c r="B126" s="54"/>
+      <c r="C126" s="68" t="s">
         <v>601</v>
       </c>
-      <c r="D126" s="64"/>
-      <c r="E126" s="64"/>
-      <c r="F126" s="64"/>
-      <c r="G126" s="64"/>
-      <c r="H126" s="64"/>
-      <c r="I126" s="64"/>
+      <c r="D126" s="54"/>
+      <c r="E126" s="54"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="54"/>
+      <c r="H126" s="54"/>
+      <c r="I126" s="54"/>
       <c r="J126" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="13.5" customHeight="1">
+    <row r="127" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B127" s="64"/>
-      <c r="C127" s="64"/>
-      <c r="D127" s="64"/>
-      <c r="E127" s="64"/>
-      <c r="F127" s="64"/>
-      <c r="G127" s="64"/>
-      <c r="H127" s="64"/>
-      <c r="I127" s="64"/>
-      <c r="J127" s="64"/>
-    </row>
-    <row r="128" spans="1:10" ht="11.25" customHeight="1">
-      <c r="A128" s="96" t="s">
+      <c r="B127" s="54"/>
+      <c r="C127" s="54"/>
+      <c r="D127" s="54"/>
+      <c r="E127" s="54"/>
+      <c r="F127" s="54"/>
+      <c r="G127" s="54"/>
+      <c r="H127" s="54"/>
+      <c r="I127" s="54"/>
+      <c r="J127" s="54"/>
+    </row>
+    <row r="128" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="53" t="s">
         <v>394</v>
       </c>
-      <c r="B128" s="64"/>
-      <c r="C128" s="64"/>
-      <c r="D128" s="64"/>
-      <c r="E128" s="64"/>
-      <c r="F128" s="64"/>
-      <c r="G128" s="64"/>
-      <c r="H128" s="64"/>
-      <c r="I128" s="64"/>
-      <c r="J128" s="64"/>
-    </row>
-    <row r="129" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A129" s="92" t="s">
+      <c r="B128" s="54"/>
+      <c r="C128" s="54"/>
+      <c r="D128" s="54"/>
+      <c r="E128" s="54"/>
+      <c r="F128" s="54"/>
+      <c r="G128" s="54"/>
+      <c r="H128" s="54"/>
+      <c r="I128" s="54"/>
+      <c r="J128" s="54"/>
+    </row>
+    <row r="129" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="B129" s="64"/>
-      <c r="C129" s="64"/>
-      <c r="D129" s="64"/>
-      <c r="E129" s="64"/>
-      <c r="F129" s="64"/>
-      <c r="G129" s="64"/>
-      <c r="H129" s="64"/>
-      <c r="I129" s="89" t="s">
+      <c r="B129" s="54"/>
+      <c r="C129" s="54"/>
+      <c r="D129" s="54"/>
+      <c r="E129" s="54"/>
+      <c r="F129" s="54"/>
+      <c r="G129" s="54"/>
+      <c r="H129" s="54"/>
+      <c r="I129" s="91" t="s">
         <v>186</v>
       </c>
-      <c r="J129" s="64"/>
-    </row>
-    <row r="130" spans="1:10" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A130" s="92" t="s">
+      <c r="J129" s="54"/>
+    </row>
+    <row r="130" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="B130" s="64"/>
-      <c r="C130" s="64"/>
-      <c r="D130" s="64"/>
-      <c r="E130" s="64"/>
-      <c r="F130" s="64"/>
-      <c r="G130" s="64"/>
-      <c r="H130" s="64"/>
-      <c r="I130" s="89" t="s">
+      <c r="B130" s="54"/>
+      <c r="C130" s="54"/>
+      <c r="D130" s="54"/>
+      <c r="E130" s="54"/>
+      <c r="F130" s="54"/>
+      <c r="G130" s="54"/>
+      <c r="H130" s="54"/>
+      <c r="I130" s="91" t="s">
         <v>223</v>
       </c>
-      <c r="J130" s="64"/>
-    </row>
-    <row r="131" spans="1:10" ht="10.5" customHeight="1">
+      <c r="J130" s="54"/>
+    </row>
+    <row r="131" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>4</v>
       </c>
@@ -6353,10 +6322,10 @@
       <c r="F131" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G131" s="75" t="s">
+      <c r="G131" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H131" s="75"/>
+      <c r="H131" s="85"/>
       <c r="I131" s="2" t="s">
         <v>11</v>
       </c>
@@ -6364,7 +6333,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="10.5" customHeight="1">
+    <row r="132" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>13</v>
       </c>
@@ -6377,16 +6346,16 @@
       <c r="D132" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E132" s="46" t="s">
+      <c r="E132" s="30" t="s">
         <v>237</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G132" s="70" t="s">
+      <c r="G132" s="58" t="s">
         <v>396</v>
       </c>
-      <c r="H132" s="71"/>
+      <c r="H132" s="59"/>
       <c r="I132" s="7" t="s">
         <v>412</v>
       </c>
@@ -6394,7 +6363,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="10.5" customHeight="1">
+    <row r="133" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>8</v>
       </c>
@@ -6404,25 +6373,25 @@
       <c r="C133" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D133" s="44" t="s">
+      <c r="D133" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E133" s="43"/>
-      <c r="F133" s="44" t="s">
+      <c r="E133" s="7"/>
+      <c r="F133" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G133" s="80" t="s">
+      <c r="G133" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="H133" s="90"/>
-      <c r="I133" s="46" t="s">
+      <c r="H133" s="107"/>
+      <c r="I133" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="J133" s="46" t="s">
+      <c r="J133" s="30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="10.5" customHeight="1">
+    <row r="134" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>7</v>
       </c>
@@ -6435,24 +6404,24 @@
       <c r="D134" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E134" s="46" t="s">
+      <c r="E134" s="30" t="s">
         <v>192</v>
       </c>
       <c r="F134" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="G134" s="85" t="s">
+      <c r="G134" s="81" t="s">
         <v>219</v>
       </c>
-      <c r="H134" s="71"/>
-      <c r="I134" s="46" t="s">
+      <c r="H134" s="59"/>
+      <c r="I134" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="J134" s="46" t="s">
+      <c r="J134" s="30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="10.5" customHeight="1">
+    <row r="135" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>13</v>
       </c>
@@ -6465,16 +6434,16 @@
       <c r="D135" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E135" s="46" t="s">
+      <c r="E135" s="30" t="s">
         <v>200</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="G135" s="70" t="s">
+      <c r="G135" s="58" t="s">
         <v>400</v>
       </c>
-      <c r="H135" s="71"/>
+      <c r="H135" s="59"/>
       <c r="I135" s="7" t="s">
         <v>149</v>
       </c>
@@ -6482,7 +6451,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="10.5" customHeight="1">
+    <row r="136" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>13</v>
       </c>
@@ -6499,10 +6468,10 @@
       <c r="F136" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="G136" s="70" t="s">
+      <c r="G136" s="58" t="s">
         <v>402</v>
       </c>
-      <c r="H136" s="71"/>
+      <c r="H136" s="59"/>
       <c r="I136" s="7" t="s">
         <v>149</v>
       </c>
@@ -6510,7 +6479,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="10.5" customHeight="1">
+    <row r="137" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>3</v>
       </c>
@@ -6520,27 +6489,27 @@
       <c r="C137" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D137" s="44" t="s">
+      <c r="D137" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E137" s="43" t="s">
+      <c r="E137" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F137" s="44" t="s">
+      <c r="F137" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G137" s="70" t="s">
+      <c r="G137" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="H137" s="71"/>
-      <c r="I137" s="43" t="s">
+      <c r="H137" s="59"/>
+      <c r="I137" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="J137" s="43" t="s">
+      <c r="J137" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="10.5" customHeight="1">
+    <row r="138" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>13</v>
       </c>
@@ -6557,10 +6526,10 @@
       <c r="F138" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G138" s="70" t="s">
+      <c r="G138" s="58" t="s">
         <v>405</v>
       </c>
-      <c r="H138" s="71"/>
+      <c r="H138" s="59"/>
       <c r="I138" s="7" t="s">
         <v>406</v>
       </c>
@@ -6568,7 +6537,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="10.5" customHeight="1">
+    <row r="139" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>13</v>
       </c>
@@ -6578,27 +6547,27 @@
       <c r="C139" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D139" s="44" t="s">
+      <c r="D139" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E139" s="43" t="s">
+      <c r="E139" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F139" s="44" t="s">
+      <c r="F139" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G139" s="70" t="s">
+      <c r="G139" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="H139" s="71"/>
-      <c r="I139" s="43" t="s">
+      <c r="H139" s="59"/>
+      <c r="I139" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="J139" s="43" t="s">
+      <c r="J139" s="7" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="140" spans="1:10" s="45" customFormat="1" ht="10.5" customHeight="1">
+    <row r="140" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>4</v>
       </c>
@@ -6611,24 +6580,24 @@
       <c r="D140" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E140" s="46" t="s">
+      <c r="E140" s="30" t="s">
         <v>204</v>
       </c>
       <c r="F140" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="G140" s="85" t="s">
+      <c r="G140" s="81" t="s">
         <v>221</v>
       </c>
-      <c r="H140" s="71"/>
-      <c r="I140" s="46" t="s">
+      <c r="H140" s="59"/>
+      <c r="I140" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="J140" s="46" t="s">
+      <c r="J140" s="30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="141" spans="1:10" s="45" customFormat="1" ht="10.5" customHeight="1">
+    <row r="141" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>413</v>
       </c>
@@ -6638,27 +6607,27 @@
       <c r="C141" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="D141" s="44" t="s">
+      <c r="D141" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E141" s="46" t="s">
+      <c r="E141" s="30" t="s">
         <v>385</v>
       </c>
-      <c r="F141" s="44" t="s">
+      <c r="F141" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G141" s="70" t="s">
+      <c r="G141" s="58" t="s">
         <v>409</v>
       </c>
-      <c r="H141" s="71"/>
-      <c r="I141" s="43" t="s">
+      <c r="H141" s="59"/>
+      <c r="I141" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="J141" s="43" t="s">
+      <c r="J141" s="7" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="142" spans="1:10" s="45" customFormat="1" ht="10.5" customHeight="1">
+    <row r="142" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>5</v>
       </c>
@@ -6671,24 +6640,24 @@
       <c r="D142" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="E142" s="43" t="s">
+      <c r="E142" s="7" t="s">
         <v>235</v>
       </c>
       <c r="F142" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="G142" s="85" t="s">
+      <c r="G142" s="81" t="s">
         <v>222</v>
       </c>
-      <c r="H142" s="71"/>
-      <c r="I142" s="46" t="s">
+      <c r="H142" s="59"/>
+      <c r="I142" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="J142" s="46" t="s">
+      <c r="J142" s="30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="10.5" customHeight="1" thickBot="1">
+    <row r="143" spans="1:10" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="8">
         <v>6</v>
       </c>
@@ -6707,10 +6676,10 @@
       <c r="F143" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="G143" s="107" t="s">
+      <c r="G143" s="94" t="s">
         <v>218</v>
       </c>
-      <c r="H143" s="88"/>
+      <c r="H143" s="95"/>
       <c r="I143" s="12" t="s">
         <v>65</v>
       </c>
@@ -6718,292 +6687,292 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="9.75" customHeight="1">
+    <row r="144" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>1</v>
       </c>
-      <c r="B144" s="61" t="s">
+      <c r="B144" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C144" s="62"/>
-      <c r="D144" s="62"/>
-      <c r="E144" s="62"/>
-      <c r="F144" s="62"/>
-      <c r="G144" s="61"/>
-      <c r="H144" s="62"/>
-      <c r="I144" s="62"/>
-      <c r="J144" s="62"/>
-    </row>
-    <row r="145" spans="1:10" ht="9.75" customHeight="1">
+      <c r="C144" s="57"/>
+      <c r="D144" s="57"/>
+      <c r="E144" s="57"/>
+      <c r="F144" s="57"/>
+      <c r="G144" s="56"/>
+      <c r="H144" s="57"/>
+      <c r="I144" s="57"/>
+      <c r="J144" s="57"/>
+    </row>
+    <row r="145" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>2</v>
       </c>
-      <c r="B145" s="61" t="s">
+      <c r="B145" s="56" t="s">
         <v>397</v>
       </c>
-      <c r="C145" s="62"/>
-      <c r="D145" s="62"/>
-      <c r="E145" s="62"/>
-      <c r="F145" s="62"/>
-      <c r="G145" s="61"/>
-      <c r="H145" s="62"/>
-      <c r="I145" s="62"/>
-      <c r="J145" s="62"/>
-    </row>
-    <row r="146" spans="1:10" ht="9.75" customHeight="1">
+      <c r="C145" s="57"/>
+      <c r="D145" s="57"/>
+      <c r="E145" s="57"/>
+      <c r="F145" s="57"/>
+      <c r="G145" s="56"/>
+      <c r="H145" s="57"/>
+      <c r="I145" s="57"/>
+      <c r="J145" s="57"/>
+    </row>
+    <row r="146" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>3</v>
       </c>
-      <c r="B146" s="61" t="s">
+      <c r="B146" s="56" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="62"/>
-      <c r="D146" s="62"/>
-      <c r="E146" s="62"/>
-      <c r="F146" s="62"/>
-      <c r="G146" s="61"/>
-      <c r="H146" s="62"/>
-      <c r="I146" s="62"/>
-      <c r="J146" s="62"/>
-    </row>
-    <row r="147" spans="1:10" ht="9.75" customHeight="1">
+      <c r="C146" s="57"/>
+      <c r="D146" s="57"/>
+      <c r="E146" s="57"/>
+      <c r="F146" s="57"/>
+      <c r="G146" s="56"/>
+      <c r="H146" s="57"/>
+      <c r="I146" s="57"/>
+      <c r="J146" s="57"/>
+    </row>
+    <row r="147" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>4</v>
       </c>
-      <c r="B147" s="61" t="s">
+      <c r="B147" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C147" s="62"/>
-      <c r="D147" s="62"/>
-      <c r="E147" s="62"/>
-      <c r="F147" s="62"/>
-      <c r="G147" s="61"/>
-      <c r="H147" s="62"/>
-      <c r="I147" s="62"/>
-      <c r="J147" s="62"/>
-    </row>
-    <row r="148" spans="1:10" ht="9.75" customHeight="1">
+      <c r="C147" s="57"/>
+      <c r="D147" s="57"/>
+      <c r="E147" s="57"/>
+      <c r="F147" s="57"/>
+      <c r="G147" s="56"/>
+      <c r="H147" s="57"/>
+      <c r="I147" s="57"/>
+      <c r="J147" s="57"/>
+    </row>
+    <row r="148" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>5</v>
       </c>
-      <c r="B148" s="61" t="s">
+      <c r="B148" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C148" s="62"/>
-      <c r="D148" s="62"/>
-      <c r="E148" s="62"/>
-      <c r="F148" s="62"/>
-      <c r="G148" s="61"/>
-      <c r="H148" s="62"/>
-      <c r="I148" s="62"/>
-      <c r="J148" s="62"/>
-    </row>
-    <row r="149" spans="1:10" ht="9.75" customHeight="1">
+      <c r="C148" s="57"/>
+      <c r="D148" s="57"/>
+      <c r="E148" s="57"/>
+      <c r="F148" s="57"/>
+      <c r="G148" s="56"/>
+      <c r="H148" s="57"/>
+      <c r="I148" s="57"/>
+      <c r="J148" s="57"/>
+    </row>
+    <row r="149" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>6</v>
       </c>
-      <c r="B149" s="61" t="s">
+      <c r="B149" s="56" t="s">
         <v>403</v>
       </c>
-      <c r="C149" s="62"/>
-      <c r="D149" s="62"/>
-      <c r="E149" s="62"/>
-      <c r="F149" s="62"/>
-      <c r="G149" s="61"/>
-      <c r="H149" s="62"/>
-      <c r="I149" s="62"/>
-      <c r="J149" s="62"/>
-    </row>
-    <row r="150" spans="1:10" ht="9.75" customHeight="1">
+      <c r="C149" s="57"/>
+      <c r="D149" s="57"/>
+      <c r="E149" s="57"/>
+      <c r="F149" s="57"/>
+      <c r="G149" s="56"/>
+      <c r="H149" s="57"/>
+      <c r="I149" s="57"/>
+      <c r="J149" s="57"/>
+    </row>
+    <row r="150" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>7</v>
       </c>
-      <c r="B150" s="61" t="s">
+      <c r="B150" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C150" s="62"/>
-      <c r="D150" s="62"/>
-      <c r="E150" s="62"/>
-      <c r="F150" s="62"/>
-      <c r="G150" s="61"/>
-      <c r="H150" s="62"/>
-      <c r="I150" s="62"/>
-      <c r="J150" s="62"/>
-    </row>
-    <row r="151" spans="1:10" ht="9.75" customHeight="1">
+      <c r="C150" s="57"/>
+      <c r="D150" s="57"/>
+      <c r="E150" s="57"/>
+      <c r="F150" s="57"/>
+      <c r="G150" s="56"/>
+      <c r="H150" s="57"/>
+      <c r="I150" s="57"/>
+      <c r="J150" s="57"/>
+    </row>
+    <row r="151" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>8</v>
       </c>
-      <c r="B151" s="61" t="s">
+      <c r="B151" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C151" s="62"/>
-      <c r="D151" s="62"/>
-      <c r="E151" s="62"/>
-      <c r="F151" s="62"/>
-      <c r="G151" s="61"/>
-      <c r="H151" s="62"/>
-      <c r="I151" s="62"/>
-      <c r="J151" s="62"/>
-    </row>
-    <row r="152" spans="1:10" s="45" customFormat="1" ht="9.75" customHeight="1">
+      <c r="C151" s="57"/>
+      <c r="D151" s="57"/>
+      <c r="E151" s="57"/>
+      <c r="F151" s="57"/>
+      <c r="G151" s="56"/>
+      <c r="H151" s="57"/>
+      <c r="I151" s="57"/>
+      <c r="J151" s="57"/>
+    </row>
+    <row r="152" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>9</v>
       </c>
-      <c r="B152" s="61" t="s">
+      <c r="B152" s="56" t="s">
         <v>407</v>
       </c>
-      <c r="C152" s="62"/>
-      <c r="D152" s="62"/>
-      <c r="E152" s="62"/>
-      <c r="F152" s="62"/>
-      <c r="G152" s="61"/>
-      <c r="H152" s="62"/>
-      <c r="I152" s="62"/>
-      <c r="J152" s="62"/>
-    </row>
-    <row r="153" spans="1:10" s="45" customFormat="1" ht="9.75" customHeight="1">
+      <c r="C152" s="57"/>
+      <c r="D152" s="57"/>
+      <c r="E152" s="57"/>
+      <c r="F152" s="57"/>
+      <c r="G152" s="56"/>
+      <c r="H152" s="57"/>
+      <c r="I152" s="57"/>
+      <c r="J152" s="57"/>
+    </row>
+    <row r="153" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>10</v>
       </c>
-      <c r="B153" s="61" t="s">
+      <c r="B153" s="56" t="s">
         <v>414</v>
       </c>
-      <c r="C153" s="62"/>
-      <c r="D153" s="62"/>
-      <c r="E153" s="62"/>
-      <c r="F153" s="62"/>
-      <c r="G153" s="61"/>
-      <c r="H153" s="62"/>
-      <c r="I153" s="62"/>
-      <c r="J153" s="62"/>
-    </row>
-    <row r="154" spans="1:10" s="45" customFormat="1" ht="9.75" customHeight="1">
+      <c r="C153" s="57"/>
+      <c r="D153" s="57"/>
+      <c r="E153" s="57"/>
+      <c r="F153" s="57"/>
+      <c r="G153" s="56"/>
+      <c r="H153" s="57"/>
+      <c r="I153" s="57"/>
+      <c r="J153" s="57"/>
+    </row>
+    <row r="154" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>11</v>
       </c>
-      <c r="B154" s="61" t="s">
+      <c r="B154" s="56" t="s">
         <v>415</v>
       </c>
-      <c r="C154" s="62"/>
-      <c r="D154" s="62"/>
-      <c r="E154" s="62"/>
-      <c r="F154" s="62"/>
-      <c r="G154" s="61"/>
-      <c r="H154" s="62"/>
-      <c r="I154" s="62"/>
-      <c r="J154" s="62"/>
-    </row>
-    <row r="155" spans="1:10" ht="9.75" customHeight="1" thickBot="1">
+      <c r="C154" s="57"/>
+      <c r="D154" s="57"/>
+      <c r="E154" s="57"/>
+      <c r="F154" s="57"/>
+      <c r="G154" s="56"/>
+      <c r="H154" s="57"/>
+      <c r="I154" s="57"/>
+      <c r="J154" s="57"/>
+    </row>
+    <row r="155" spans="1:10" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="9">
         <v>12</v>
       </c>
-      <c r="B155" s="106" t="s">
+      <c r="B155" s="83" t="s">
         <v>416</v>
       </c>
       <c r="C155" s="84"/>
       <c r="D155" s="84"/>
       <c r="E155" s="84"/>
       <c r="F155" s="84"/>
-      <c r="G155" s="106"/>
+      <c r="G155" s="83"/>
       <c r="H155" s="84"/>
       <c r="I155" s="84"/>
       <c r="J155" s="84"/>
     </row>
-    <row r="156" spans="1:10" ht="3" customHeight="1"/>
-    <row r="157" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A157" s="66" t="s">
+    <row r="156" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="B157" s="64"/>
-      <c r="C157" s="63" t="s">
+      <c r="B157" s="54"/>
+      <c r="C157" s="68" t="s">
         <v>602</v>
       </c>
-      <c r="D157" s="64"/>
-      <c r="E157" s="64"/>
-      <c r="F157" s="64"/>
-      <c r="G157" s="64"/>
-      <c r="H157" s="64"/>
-      <c r="I157" s="64"/>
+      <c r="D157" s="54"/>
+      <c r="E157" s="54"/>
+      <c r="F157" s="54"/>
+      <c r="G157" s="54"/>
+      <c r="H157" s="54"/>
+      <c r="I157" s="54"/>
       <c r="J157" s="1" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="13.5" customHeight="1">
+    <row r="158" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B158" s="64"/>
-      <c r="C158" s="64"/>
-      <c r="D158" s="64"/>
-      <c r="E158" s="64"/>
-      <c r="F158" s="64"/>
-      <c r="G158" s="64"/>
-      <c r="H158" s="64"/>
-      <c r="I158" s="64"/>
-      <c r="J158" s="64"/>
-    </row>
-    <row r="159" spans="1:10" ht="12" customHeight="1">
-      <c r="A159" s="96" t="s">
+      <c r="B158" s="54"/>
+      <c r="C158" s="54"/>
+      <c r="D158" s="54"/>
+      <c r="E158" s="54"/>
+      <c r="F158" s="54"/>
+      <c r="G158" s="54"/>
+      <c r="H158" s="54"/>
+      <c r="I158" s="54"/>
+      <c r="J158" s="54"/>
+    </row>
+    <row r="159" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="53" t="s">
         <v>417</v>
       </c>
-      <c r="B159" s="64"/>
-      <c r="C159" s="64"/>
-      <c r="D159" s="64"/>
-      <c r="E159" s="64"/>
-      <c r="F159" s="64"/>
-      <c r="G159" s="64"/>
-      <c r="H159" s="64"/>
-      <c r="I159" s="64"/>
-      <c r="J159" s="64"/>
-    </row>
-    <row r="160" spans="1:10" s="45" customFormat="1" ht="12" customHeight="1">
-      <c r="A160" s="103" t="s">
+      <c r="B159" s="54"/>
+      <c r="C159" s="54"/>
+      <c r="D159" s="54"/>
+      <c r="E159" s="54"/>
+      <c r="F159" s="54"/>
+      <c r="G159" s="54"/>
+      <c r="H159" s="54"/>
+      <c r="I159" s="54"/>
+      <c r="J159" s="54"/>
+    </row>
+    <row r="160" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="106" t="s">
         <v>418</v>
       </c>
-      <c r="B160" s="103"/>
-      <c r="C160" s="103"/>
-      <c r="D160" s="103"/>
-      <c r="E160" s="103"/>
-      <c r="F160" s="103"/>
-      <c r="G160" s="103"/>
-      <c r="H160" s="103"/>
-      <c r="I160" s="103"/>
-      <c r="J160" s="103"/>
-    </row>
-    <row r="161" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A161" s="92" t="s">
+      <c r="B160" s="106"/>
+      <c r="C160" s="106"/>
+      <c r="D160" s="106"/>
+      <c r="E160" s="106"/>
+      <c r="F160" s="106"/>
+      <c r="G160" s="106"/>
+      <c r="H160" s="106"/>
+      <c r="I160" s="106"/>
+      <c r="J160" s="106"/>
+    </row>
+    <row r="161" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="64" t="s">
         <v>419</v>
       </c>
-      <c r="B161" s="64"/>
-      <c r="C161" s="64"/>
-      <c r="D161" s="64"/>
-      <c r="E161" s="64"/>
-      <c r="F161" s="64"/>
-      <c r="G161" s="64"/>
-      <c r="H161" s="64"/>
-      <c r="I161" s="91" t="s">
+      <c r="B161" s="54"/>
+      <c r="C161" s="54"/>
+      <c r="D161" s="54"/>
+      <c r="E161" s="54"/>
+      <c r="F161" s="54"/>
+      <c r="G161" s="54"/>
+      <c r="H161" s="54"/>
+      <c r="I161" s="55" t="s">
         <v>187</v>
       </c>
-      <c r="J161" s="64"/>
-    </row>
-    <row r="162" spans="1:10" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A162" s="92" t="s">
+      <c r="J161" s="54"/>
+    </row>
+    <row r="162" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="B162" s="64"/>
-      <c r="C162" s="64"/>
-      <c r="D162" s="64"/>
-      <c r="E162" s="64"/>
-      <c r="F162" s="64"/>
-      <c r="G162" s="64"/>
-      <c r="H162" s="64"/>
-      <c r="I162" s="91" t="s">
+      <c r="B162" s="54"/>
+      <c r="C162" s="54"/>
+      <c r="D162" s="54"/>
+      <c r="E162" s="54"/>
+      <c r="F162" s="54"/>
+      <c r="G162" s="54"/>
+      <c r="H162" s="54"/>
+      <c r="I162" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="J162" s="64"/>
-    </row>
-    <row r="163" spans="1:10" ht="9.75" customHeight="1">
+      <c r="J162" s="54"/>
+    </row>
+    <row r="163" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>4</v>
       </c>
@@ -7022,10 +6991,10 @@
       <c r="F163" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G163" s="75" t="s">
+      <c r="G163" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H163" s="75"/>
+      <c r="H163" s="85"/>
       <c r="I163" s="2" t="s">
         <v>11</v>
       </c>
@@ -7033,7 +7002,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="9.75" customHeight="1">
+    <row r="164" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>424</v>
       </c>
@@ -7052,10 +7021,10 @@
       <c r="F164" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G164" s="70" t="s">
+      <c r="G164" s="58" t="s">
         <v>421</v>
       </c>
-      <c r="H164" s="71"/>
+      <c r="H164" s="59"/>
       <c r="I164" s="7" t="s">
         <v>422</v>
       </c>
@@ -7063,7 +7032,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="9.75" customHeight="1">
+    <row r="165" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>427</v>
       </c>
@@ -7082,10 +7051,10 @@
       <c r="F165" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G165" s="70" t="s">
+      <c r="G165" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="H165" s="71"/>
+      <c r="H165" s="59"/>
       <c r="I165" s="30" t="s">
         <v>76</v>
       </c>
@@ -7093,7 +7062,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="9.75" customHeight="1">
+    <row r="166" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>431</v>
       </c>
@@ -7103,27 +7072,27 @@
       <c r="C166" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D166" s="44" t="s">
+      <c r="D166" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E166" s="43" t="s">
+      <c r="E166" s="7" t="s">
         <v>202</v>
       </c>
       <c r="F166" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="G166" s="70" t="s">
+      <c r="G166" s="58" t="s">
         <v>430</v>
       </c>
-      <c r="H166" s="71"/>
-      <c r="I166" s="43" t="s">
+      <c r="H166" s="59"/>
+      <c r="I166" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J166" s="43" t="s">
+      <c r="J166" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="9.75" customHeight="1">
+    <row r="167" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>436</v>
       </c>
@@ -7142,10 +7111,10 @@
       <c r="F167" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="G167" s="70" t="s">
+      <c r="G167" s="58" t="s">
         <v>435</v>
       </c>
-      <c r="H167" s="71"/>
+      <c r="H167" s="59"/>
       <c r="I167" s="7" t="s">
         <v>139</v>
       </c>
@@ -7153,7 +7122,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="9.75" customHeight="1">
+    <row r="168" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>442</v>
       </c>
@@ -7172,10 +7141,10 @@
       <c r="F168" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G168" s="80" t="s">
+      <c r="G168" s="66" t="s">
         <v>441</v>
       </c>
-      <c r="H168" s="90"/>
+      <c r="H168" s="107"/>
       <c r="I168" s="30" t="s">
         <v>139</v>
       </c>
@@ -7183,7 +7152,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="9.75" customHeight="1">
+    <row r="169" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>447</v>
       </c>
@@ -7202,10 +7171,10 @@
       <c r="F169" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="G169" s="85" t="s">
+      <c r="G169" s="81" t="s">
         <v>446</v>
       </c>
-      <c r="H169" s="71"/>
+      <c r="H169" s="59"/>
       <c r="I169" s="30" t="s">
         <v>608</v>
       </c>
@@ -7213,7 +7182,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="9.75" customHeight="1" thickBot="1">
+    <row r="170" spans="1:10" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="8" t="s">
         <v>78</v>
       </c>
@@ -7232,10 +7201,10 @@
       <c r="F170" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="G170" s="87" t="s">
+      <c r="G170" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="H170" s="88"/>
+      <c r="H170" s="95"/>
       <c r="I170" s="32" t="s">
         <v>81</v>
       </c>
@@ -7243,226 +7212,226 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="9.75" customHeight="1">
+    <row r="171" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>1</v>
       </c>
-      <c r="B171" s="61" t="s">
+      <c r="B171" s="56" t="s">
         <v>425</v>
       </c>
-      <c r="C171" s="62"/>
-      <c r="D171" s="62"/>
-      <c r="E171" s="62"/>
-      <c r="F171" s="62"/>
-      <c r="G171" s="61" t="s">
+      <c r="C171" s="57"/>
+      <c r="D171" s="57"/>
+      <c r="E171" s="57"/>
+      <c r="F171" s="57"/>
+      <c r="G171" s="56" t="s">
         <v>426</v>
       </c>
-      <c r="H171" s="62"/>
-      <c r="I171" s="62"/>
-      <c r="J171" s="62"/>
-    </row>
-    <row r="172" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H171" s="57"/>
+      <c r="I171" s="57"/>
+      <c r="J171" s="57"/>
+    </row>
+    <row r="172" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>2</v>
       </c>
-      <c r="B172" s="61" t="s">
+      <c r="B172" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="C172" s="62"/>
-      <c r="D172" s="62"/>
-      <c r="E172" s="62"/>
-      <c r="F172" s="62"/>
-      <c r="G172" s="61" t="s">
+      <c r="C172" s="57"/>
+      <c r="D172" s="57"/>
+      <c r="E172" s="57"/>
+      <c r="F172" s="57"/>
+      <c r="G172" s="56" t="s">
         <v>428</v>
       </c>
-      <c r="H172" s="62"/>
-      <c r="I172" s="62"/>
-      <c r="J172" s="62"/>
-    </row>
-    <row r="173" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H172" s="57"/>
+      <c r="I172" s="57"/>
+      <c r="J172" s="57"/>
+    </row>
+    <row r="173" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>3</v>
       </c>
-      <c r="B173" s="61" t="s">
+      <c r="B173" s="56" t="s">
         <v>432</v>
       </c>
-      <c r="C173" s="62"/>
-      <c r="D173" s="62"/>
-      <c r="E173" s="62"/>
-      <c r="F173" s="62"/>
-      <c r="G173" s="61" t="s">
+      <c r="C173" s="57"/>
+      <c r="D173" s="57"/>
+      <c r="E173" s="57"/>
+      <c r="F173" s="57"/>
+      <c r="G173" s="56" t="s">
         <v>433</v>
       </c>
-      <c r="H173" s="62"/>
-      <c r="I173" s="62"/>
-      <c r="J173" s="62"/>
-    </row>
-    <row r="174" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H173" s="57"/>
+      <c r="I173" s="57"/>
+      <c r="J173" s="57"/>
+    </row>
+    <row r="174" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>4</v>
       </c>
-      <c r="B174" s="99" t="s">
+      <c r="B174" s="108" t="s">
         <v>438</v>
       </c>
-      <c r="C174" s="100"/>
-      <c r="D174" s="100"/>
-      <c r="E174" s="100"/>
-      <c r="F174" s="101"/>
-      <c r="G174" s="61" t="s">
+      <c r="C174" s="109"/>
+      <c r="D174" s="109"/>
+      <c r="E174" s="109"/>
+      <c r="F174" s="110"/>
+      <c r="G174" s="56" t="s">
         <v>439</v>
       </c>
-      <c r="H174" s="62"/>
-      <c r="I174" s="62"/>
-      <c r="J174" s="62"/>
-    </row>
-    <row r="175" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H174" s="57"/>
+      <c r="I174" s="57"/>
+      <c r="J174" s="57"/>
+    </row>
+    <row r="175" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>5</v>
       </c>
-      <c r="B175" s="61" t="s">
+      <c r="B175" s="56" t="s">
         <v>443</v>
       </c>
-      <c r="C175" s="62"/>
-      <c r="D175" s="62"/>
-      <c r="E175" s="62"/>
-      <c r="F175" s="62"/>
-      <c r="G175" s="61" t="s">
+      <c r="C175" s="57"/>
+      <c r="D175" s="57"/>
+      <c r="E175" s="57"/>
+      <c r="F175" s="57"/>
+      <c r="G175" s="56" t="s">
         <v>444</v>
       </c>
-      <c r="H175" s="62"/>
-      <c r="I175" s="62"/>
-      <c r="J175" s="62"/>
-    </row>
-    <row r="176" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H175" s="57"/>
+      <c r="I175" s="57"/>
+      <c r="J175" s="57"/>
+    </row>
+    <row r="176" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>6</v>
       </c>
-      <c r="B176" s="61" t="s">
+      <c r="B176" s="56" t="s">
         <v>448</v>
       </c>
-      <c r="C176" s="62"/>
-      <c r="D176" s="62"/>
-      <c r="E176" s="62"/>
-      <c r="F176" s="62"/>
-      <c r="G176" s="61" t="s">
+      <c r="C176" s="57"/>
+      <c r="D176" s="57"/>
+      <c r="E176" s="57"/>
+      <c r="F176" s="57"/>
+      <c r="G176" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="H176" s="62"/>
-      <c r="I176" s="62"/>
-      <c r="J176" s="62"/>
-    </row>
-    <row r="177" spans="1:10" ht="9.75" customHeight="1" thickBot="1">
+      <c r="H176" s="57"/>
+      <c r="I176" s="57"/>
+      <c r="J176" s="57"/>
+    </row>
+    <row r="177" spans="1:10" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="9">
         <v>7</v>
       </c>
-      <c r="B177" s="106" t="s">
+      <c r="B177" s="83" t="s">
         <v>94</v>
       </c>
       <c r="C177" s="84"/>
       <c r="D177" s="84"/>
       <c r="E177" s="84"/>
       <c r="F177" s="84"/>
-      <c r="G177" s="106" t="s">
+      <c r="G177" s="83" t="s">
         <v>95</v>
       </c>
       <c r="H177" s="84"/>
       <c r="I177" s="84"/>
       <c r="J177" s="84"/>
     </row>
-    <row r="178" spans="1:10" ht="3" customHeight="1"/>
-    <row r="179" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A179" s="66" t="s">
+    <row r="178" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="B179" s="64"/>
-      <c r="C179" s="63" t="s">
+      <c r="B179" s="54"/>
+      <c r="C179" s="68" t="s">
         <v>603</v>
       </c>
-      <c r="D179" s="64"/>
-      <c r="E179" s="64"/>
-      <c r="F179" s="64"/>
-      <c r="G179" s="64"/>
-      <c r="H179" s="64"/>
-      <c r="I179" s="64"/>
+      <c r="D179" s="54"/>
+      <c r="E179" s="54"/>
+      <c r="F179" s="54"/>
+      <c r="G179" s="54"/>
+      <c r="H179" s="54"/>
+      <c r="I179" s="54"/>
       <c r="J179" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="13.5" customHeight="1">
+    <row r="180" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="B180" s="64"/>
-      <c r="C180" s="64"/>
-      <c r="D180" s="64"/>
-      <c r="E180" s="64"/>
-      <c r="F180" s="64"/>
-      <c r="G180" s="64"/>
-      <c r="H180" s="64"/>
-      <c r="I180" s="64"/>
-      <c r="J180" s="64"/>
-    </row>
-    <row r="181" spans="1:10" ht="12" customHeight="1">
-      <c r="A181" s="96" t="s">
+      <c r="B180" s="54"/>
+      <c r="C180" s="54"/>
+      <c r="D180" s="54"/>
+      <c r="E180" s="54"/>
+      <c r="F180" s="54"/>
+      <c r="G180" s="54"/>
+      <c r="H180" s="54"/>
+      <c r="I180" s="54"/>
+      <c r="J180" s="54"/>
+    </row>
+    <row r="181" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="53" t="s">
         <v>450</v>
       </c>
-      <c r="B181" s="64"/>
-      <c r="C181" s="64"/>
-      <c r="D181" s="64"/>
-      <c r="E181" s="64"/>
-      <c r="F181" s="64"/>
-      <c r="G181" s="64"/>
-      <c r="H181" s="64"/>
-      <c r="I181" s="64"/>
-      <c r="J181" s="64"/>
-    </row>
-    <row r="182" spans="1:10" s="45" customFormat="1" ht="12" customHeight="1">
-      <c r="A182" s="103" t="s">
+      <c r="B181" s="54"/>
+      <c r="C181" s="54"/>
+      <c r="D181" s="54"/>
+      <c r="E181" s="54"/>
+      <c r="F181" s="54"/>
+      <c r="G181" s="54"/>
+      <c r="H181" s="54"/>
+      <c r="I181" s="54"/>
+      <c r="J181" s="54"/>
+    </row>
+    <row r="182" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="106" t="s">
         <v>451</v>
       </c>
-      <c r="B182" s="103"/>
-      <c r="C182" s="103"/>
-      <c r="D182" s="103"/>
-      <c r="E182" s="103"/>
-      <c r="F182" s="103"/>
-      <c r="G182" s="103"/>
-      <c r="H182" s="103"/>
-      <c r="I182" s="103"/>
-      <c r="J182" s="103"/>
-    </row>
-    <row r="183" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A183" s="92" t="s">
+      <c r="B182" s="106"/>
+      <c r="C182" s="106"/>
+      <c r="D182" s="106"/>
+      <c r="E182" s="106"/>
+      <c r="F182" s="106"/>
+      <c r="G182" s="106"/>
+      <c r="H182" s="106"/>
+      <c r="I182" s="106"/>
+      <c r="J182" s="106"/>
+    </row>
+    <row r="183" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="B183" s="64"/>
-      <c r="C183" s="64"/>
-      <c r="D183" s="64"/>
-      <c r="E183" s="64"/>
-      <c r="F183" s="64"/>
-      <c r="G183" s="64"/>
-      <c r="H183" s="64"/>
-      <c r="I183" s="89" t="s">
+      <c r="B183" s="54"/>
+      <c r="C183" s="54"/>
+      <c r="D183" s="54"/>
+      <c r="E183" s="54"/>
+      <c r="F183" s="54"/>
+      <c r="G183" s="54"/>
+      <c r="H183" s="54"/>
+      <c r="I183" s="91" t="s">
         <v>188</v>
       </c>
-      <c r="J183" s="64"/>
-    </row>
-    <row r="184" spans="1:10" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A184" s="92" t="s">
+      <c r="J183" s="54"/>
+    </row>
+    <row r="184" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="B184" s="64"/>
-      <c r="C184" s="64"/>
-      <c r="D184" s="64"/>
-      <c r="E184" s="64"/>
-      <c r="F184" s="64"/>
-      <c r="G184" s="64"/>
-      <c r="H184" s="64"/>
-      <c r="I184" s="89" t="s">
+      <c r="B184" s="54"/>
+      <c r="C184" s="54"/>
+      <c r="D184" s="54"/>
+      <c r="E184" s="54"/>
+      <c r="F184" s="54"/>
+      <c r="G184" s="54"/>
+      <c r="H184" s="54"/>
+      <c r="I184" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="J184" s="64"/>
-    </row>
-    <row r="185" spans="1:10" ht="9.75" customHeight="1">
+      <c r="J184" s="54"/>
+    </row>
+    <row r="185" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>4</v>
       </c>
@@ -7481,10 +7450,10 @@
       <c r="F185" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G185" s="75" t="s">
+      <c r="G185" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H185" s="75"/>
+      <c r="H185" s="85"/>
       <c r="I185" s="2" t="s">
         <v>11</v>
       </c>
@@ -7492,7 +7461,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="9.75" customHeight="1">
+    <row r="186" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>455</v>
       </c>
@@ -7502,118 +7471,118 @@
       <c r="C186" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="D186" s="44" t="s">
+      <c r="D186" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E186" s="46" t="s">
+      <c r="E186" s="30" t="s">
         <v>234</v>
       </c>
       <c r="F186" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="G186" s="70" t="s">
+      <c r="G186" s="58" t="s">
         <v>454</v>
       </c>
-      <c r="H186" s="71"/>
-      <c r="I186" s="43" t="s">
+      <c r="H186" s="59"/>
+      <c r="I186" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="J186" s="43" t="s">
+      <c r="J186" s="7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A187" s="48" t="s">
+    <row r="187" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="37" t="s">
         <v>460</v>
       </c>
-      <c r="B187" s="51">
+      <c r="B187" s="39">
         <v>2</v>
       </c>
-      <c r="C187" s="52" t="s">
+      <c r="C187" s="40" t="s">
         <v>458</v>
       </c>
       <c r="D187" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E187" s="46" t="s">
+      <c r="E187" s="30" t="s">
         <v>235</v>
       </c>
       <c r="F187" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="G187" s="85" t="s">
+      <c r="G187" s="81" t="s">
         <v>459</v>
       </c>
-      <c r="H187" s="86"/>
-      <c r="I187" s="46" t="s">
+      <c r="H187" s="82"/>
+      <c r="I187" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="J187" s="46" t="s">
+      <c r="J187" s="30" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A188" s="48" t="s">
+    <row r="188" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="37" t="s">
         <v>463</v>
       </c>
-      <c r="B188" s="51">
+      <c r="B188" s="39">
         <v>3</v>
       </c>
-      <c r="C188" s="52" t="s">
+      <c r="C188" s="40" t="s">
         <v>106</v>
       </c>
       <c r="D188" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="E188" s="46" t="s">
+      <c r="E188" s="30" t="s">
         <v>204</v>
       </c>
       <c r="F188" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="G188" s="85" t="s">
+      <c r="G188" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="H188" s="86"/>
-      <c r="I188" s="46" t="s">
+      <c r="H188" s="82"/>
+      <c r="I188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="J188" s="46" t="s">
+      <c r="J188" s="30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A189" s="48" t="s">
+    <row r="189" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="B189" s="51">
+      <c r="B189" s="39">
         <v>4</v>
       </c>
-      <c r="C189" s="52" t="s">
+      <c r="C189" s="40" t="s">
         <v>465</v>
       </c>
       <c r="D189" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="E189" s="46" t="s">
+      <c r="E189" s="30" t="s">
         <v>200</v>
       </c>
       <c r="F189" s="31" t="s">
         <v>468</v>
       </c>
-      <c r="G189" s="85" t="s">
+      <c r="G189" s="81" t="s">
         <v>466</v>
       </c>
-      <c r="H189" s="86"/>
-      <c r="I189" s="46" t="s">
+      <c r="H189" s="82"/>
+      <c r="I189" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="J189" s="46" t="s">
+      <c r="J189" s="30" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A190" s="48" t="s">
+    <row r="190" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="37" t="s">
         <v>473</v>
       </c>
       <c r="B190" s="4">
@@ -7625,16 +7594,16 @@
       <c r="D190" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E190" s="46" t="s">
+      <c r="E190" s="30" t="s">
         <v>193</v>
       </c>
       <c r="F190" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="G190" s="70" t="s">
+      <c r="G190" s="58" t="s">
         <v>472</v>
       </c>
-      <c r="H190" s="71"/>
+      <c r="H190" s="59"/>
       <c r="I190" s="7" t="s">
         <v>65</v>
       </c>
@@ -7642,66 +7611,66 @@
         <v>66</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A191" s="48" t="s">
+    <row r="191" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="37" t="s">
         <v>478</v>
       </c>
-      <c r="B191" s="51">
+      <c r="B191" s="39">
         <v>6</v>
       </c>
-      <c r="C191" s="52" t="s">
+      <c r="C191" s="40" t="s">
         <v>476</v>
       </c>
       <c r="D191" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E191" s="46" t="s">
+      <c r="E191" s="30" t="s">
         <v>198</v>
       </c>
       <c r="F191" s="31" t="s">
         <v>468</v>
       </c>
-      <c r="G191" s="85" t="s">
+      <c r="G191" s="81" t="s">
         <v>477</v>
       </c>
-      <c r="H191" s="86"/>
-      <c r="I191" s="46" t="s">
+      <c r="H191" s="82"/>
+      <c r="I191" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="J191" s="46" t="s">
+      <c r="J191" s="30" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A192" s="48" t="s">
+    <row r="192" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="37" t="s">
         <v>483</v>
       </c>
-      <c r="B192" s="51">
+      <c r="B192" s="39">
         <v>7</v>
       </c>
-      <c r="C192" s="52" t="s">
+      <c r="C192" s="40" t="s">
         <v>481</v>
       </c>
       <c r="D192" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E192" s="46"/>
+      <c r="E192" s="30"/>
       <c r="F192" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="G192" s="85" t="s">
+      <c r="G192" s="81" t="s">
         <v>482</v>
       </c>
-      <c r="H192" s="86"/>
-      <c r="I192" s="46" t="s">
+      <c r="H192" s="82"/>
+      <c r="I192" s="30" t="s">
         <v>376</v>
       </c>
-      <c r="J192" s="46" t="s">
+      <c r="J192" s="30" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="9.75" customHeight="1" thickBot="1">
-      <c r="A193" s="54" t="s">
+    <row r="193" spans="1:10" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="42" t="s">
         <v>488</v>
       </c>
       <c r="B193" s="9">
@@ -7713,16 +7682,16 @@
       <c r="D193" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E193" s="47" t="s">
+      <c r="E193" s="32" t="s">
         <v>203</v>
       </c>
       <c r="F193" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="G193" s="107" t="s">
+      <c r="G193" s="94" t="s">
         <v>487</v>
       </c>
-      <c r="H193" s="88"/>
+      <c r="H193" s="95"/>
       <c r="I193" s="12" t="s">
         <v>63</v>
       </c>
@@ -7730,230 +7699,230 @@
         <v>64</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="9.75" customHeight="1">
+    <row r="194" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>1</v>
       </c>
-      <c r="B194" s="61" t="s">
+      <c r="B194" s="56" t="s">
         <v>456</v>
       </c>
-      <c r="C194" s="62"/>
-      <c r="D194" s="62"/>
-      <c r="E194" s="62"/>
-      <c r="F194" s="62"/>
-      <c r="G194" s="80" t="s">
+      <c r="C194" s="57"/>
+      <c r="D194" s="57"/>
+      <c r="E194" s="57"/>
+      <c r="F194" s="57"/>
+      <c r="G194" s="66" t="s">
         <v>457</v>
       </c>
-      <c r="H194" s="62"/>
-      <c r="I194" s="62"/>
-      <c r="J194" s="62"/>
-    </row>
-    <row r="195" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H194" s="57"/>
+      <c r="I194" s="57"/>
+      <c r="J194" s="57"/>
+    </row>
+    <row r="195" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>2</v>
       </c>
-      <c r="B195" s="80" t="s">
+      <c r="B195" s="66" t="s">
         <v>461</v>
       </c>
-      <c r="C195" s="62"/>
-      <c r="D195" s="62"/>
-      <c r="E195" s="62"/>
-      <c r="F195" s="62"/>
-      <c r="G195" s="80" t="s">
+      <c r="C195" s="57"/>
+      <c r="D195" s="57"/>
+      <c r="E195" s="57"/>
+      <c r="F195" s="57"/>
+      <c r="G195" s="66" t="s">
         <v>462</v>
       </c>
-      <c r="H195" s="62"/>
-      <c r="I195" s="62"/>
-      <c r="J195" s="62"/>
-    </row>
-    <row r="196" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H195" s="57"/>
+      <c r="I195" s="57"/>
+      <c r="J195" s="57"/>
+    </row>
+    <row r="196" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>3</v>
       </c>
-      <c r="B196" s="80" t="s">
+      <c r="B196" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="C196" s="62"/>
-      <c r="D196" s="62"/>
-      <c r="E196" s="62"/>
-      <c r="F196" s="62"/>
-      <c r="G196" s="80" t="s">
+      <c r="C196" s="57"/>
+      <c r="D196" s="57"/>
+      <c r="E196" s="57"/>
+      <c r="F196" s="57"/>
+      <c r="G196" s="66" t="s">
         <v>464</v>
       </c>
-      <c r="H196" s="62"/>
-      <c r="I196" s="62"/>
-      <c r="J196" s="62"/>
-    </row>
-    <row r="197" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H196" s="57"/>
+      <c r="I196" s="57"/>
+      <c r="J196" s="57"/>
+    </row>
+    <row r="197" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>4</v>
       </c>
-      <c r="B197" s="80" t="s">
+      <c r="B197" s="66" t="s">
         <v>469</v>
       </c>
-      <c r="C197" s="62"/>
-      <c r="D197" s="62"/>
-      <c r="E197" s="62"/>
-      <c r="F197" s="62"/>
-      <c r="G197" s="80" t="s">
+      <c r="C197" s="57"/>
+      <c r="D197" s="57"/>
+      <c r="E197" s="57"/>
+      <c r="F197" s="57"/>
+      <c r="G197" s="66" t="s">
         <v>470</v>
       </c>
-      <c r="H197" s="62"/>
-      <c r="I197" s="62"/>
-      <c r="J197" s="62"/>
-    </row>
-    <row r="198" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H197" s="57"/>
+      <c r="I197" s="57"/>
+      <c r="J197" s="57"/>
+    </row>
+    <row r="198" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>5</v>
       </c>
-      <c r="B198" s="80" t="s">
+      <c r="B198" s="66" t="s">
         <v>474</v>
       </c>
-      <c r="C198" s="62"/>
-      <c r="D198" s="62"/>
-      <c r="E198" s="62"/>
-      <c r="F198" s="62"/>
-      <c r="G198" s="80" t="s">
+      <c r="C198" s="57"/>
+      <c r="D198" s="57"/>
+      <c r="E198" s="57"/>
+      <c r="F198" s="57"/>
+      <c r="G198" s="66" t="s">
         <v>475</v>
       </c>
-      <c r="H198" s="62"/>
-      <c r="I198" s="62"/>
-      <c r="J198" s="62"/>
-    </row>
-    <row r="199" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H198" s="57"/>
+      <c r="I198" s="57"/>
+      <c r="J198" s="57"/>
+    </row>
+    <row r="199" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>6</v>
       </c>
-      <c r="B199" s="80" t="s">
+      <c r="B199" s="66" t="s">
         <v>479</v>
       </c>
-      <c r="C199" s="62"/>
-      <c r="D199" s="62"/>
-      <c r="E199" s="62"/>
-      <c r="F199" s="62"/>
-      <c r="G199" s="80" t="s">
+      <c r="C199" s="57"/>
+      <c r="D199" s="57"/>
+      <c r="E199" s="57"/>
+      <c r="F199" s="57"/>
+      <c r="G199" s="66" t="s">
         <v>480</v>
       </c>
-      <c r="H199" s="62"/>
-      <c r="I199" s="62"/>
-      <c r="J199" s="62"/>
-    </row>
-    <row r="200" spans="1:10" ht="9.75" customHeight="1">
+      <c r="H199" s="57"/>
+      <c r="I199" s="57"/>
+      <c r="J199" s="57"/>
+    </row>
+    <row r="200" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>7</v>
       </c>
-      <c r="B200" s="80" t="s">
+      <c r="B200" s="66" t="s">
         <v>484</v>
       </c>
-      <c r="C200" s="62"/>
-      <c r="D200" s="62"/>
-      <c r="E200" s="62"/>
-      <c r="F200" s="62"/>
-      <c r="G200" s="80" t="s">
+      <c r="C200" s="57"/>
+      <c r="D200" s="57"/>
+      <c r="E200" s="57"/>
+      <c r="F200" s="57"/>
+      <c r="G200" s="66" t="s">
         <v>485</v>
       </c>
-      <c r="H200" s="62"/>
-      <c r="I200" s="62"/>
-      <c r="J200" s="62"/>
-    </row>
-    <row r="201" spans="1:10" ht="9.75" customHeight="1" thickBot="1">
+      <c r="H200" s="57"/>
+      <c r="I200" s="57"/>
+      <c r="J200" s="57"/>
+    </row>
+    <row r="201" spans="1:10" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="9">
         <v>8</v>
       </c>
-      <c r="B201" s="83" t="s">
+      <c r="B201" s="90" t="s">
         <v>489</v>
       </c>
       <c r="C201" s="84"/>
       <c r="D201" s="84"/>
       <c r="E201" s="84"/>
       <c r="F201" s="84"/>
-      <c r="G201" s="83" t="s">
+      <c r="G201" s="90" t="s">
         <v>490</v>
       </c>
       <c r="H201" s="84"/>
       <c r="I201" s="84"/>
       <c r="J201" s="84"/>
     </row>
-    <row r="202" spans="1:10" ht="9" customHeight="1"/>
-    <row r="203" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A203" s="66" t="s">
+    <row r="202" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="B203" s="64"/>
-      <c r="C203" s="63" t="s">
+      <c r="B203" s="54"/>
+      <c r="C203" s="68" t="s">
         <v>604</v>
       </c>
-      <c r="D203" s="64"/>
-      <c r="E203" s="64"/>
-      <c r="F203" s="64"/>
-      <c r="G203" s="64"/>
-      <c r="H203" s="64"/>
-      <c r="I203" s="64"/>
-      <c r="J203" s="53" t="s">
+      <c r="D203" s="54"/>
+      <c r="E203" s="54"/>
+      <c r="F203" s="54"/>
+      <c r="G203" s="54"/>
+      <c r="H203" s="54"/>
+      <c r="I203" s="54"/>
+      <c r="J203" s="41" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="13.5" customHeight="1">
+    <row r="204" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B204" s="64"/>
-      <c r="C204" s="64"/>
-      <c r="D204" s="64"/>
-      <c r="E204" s="64"/>
-      <c r="F204" s="64"/>
-      <c r="G204" s="64"/>
-      <c r="H204" s="64"/>
-      <c r="I204" s="64"/>
-      <c r="J204" s="64"/>
-    </row>
-    <row r="205" spans="1:10" ht="11.25" customHeight="1">
-      <c r="A205" s="96" t="s">
+      <c r="B204" s="54"/>
+      <c r="C204" s="54"/>
+      <c r="D204" s="54"/>
+      <c r="E204" s="54"/>
+      <c r="F204" s="54"/>
+      <c r="G204" s="54"/>
+      <c r="H204" s="54"/>
+      <c r="I204" s="54"/>
+      <c r="J204" s="54"/>
+    </row>
+    <row r="205" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="53" t="s">
         <v>492</v>
       </c>
-      <c r="B205" s="64"/>
-      <c r="C205" s="64"/>
-      <c r="D205" s="64"/>
-      <c r="E205" s="64"/>
-      <c r="F205" s="64"/>
-      <c r="G205" s="64"/>
-      <c r="H205" s="64"/>
-      <c r="I205" s="64"/>
-      <c r="J205" s="64"/>
-    </row>
-    <row r="206" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A206" s="102" t="s">
+      <c r="B205" s="54"/>
+      <c r="C205" s="54"/>
+      <c r="D205" s="54"/>
+      <c r="E205" s="54"/>
+      <c r="F205" s="54"/>
+      <c r="G205" s="54"/>
+      <c r="H205" s="54"/>
+      <c r="I205" s="54"/>
+      <c r="J205" s="54"/>
+    </row>
+    <row r="206" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="60" t="s">
         <v>296</v>
       </c>
-      <c r="B206" s="64"/>
-      <c r="C206" s="64"/>
-      <c r="D206" s="64"/>
-      <c r="E206" s="64"/>
-      <c r="F206" s="64"/>
-      <c r="G206" s="64"/>
-      <c r="H206" s="64"/>
-      <c r="I206" s="91" t="s">
+      <c r="B206" s="54"/>
+      <c r="C206" s="54"/>
+      <c r="D206" s="54"/>
+      <c r="E206" s="54"/>
+      <c r="F206" s="54"/>
+      <c r="G206" s="54"/>
+      <c r="H206" s="54"/>
+      <c r="I206" s="55" t="s">
         <v>185</v>
       </c>
-      <c r="J206" s="64"/>
-    </row>
-    <row r="207" spans="1:10" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A207" s="92" t="s">
+      <c r="J206" s="54"/>
+    </row>
+    <row r="207" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A207" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B207" s="64"/>
-      <c r="C207" s="64"/>
-      <c r="D207" s="64"/>
-      <c r="E207" s="64"/>
-      <c r="F207" s="64"/>
-      <c r="G207" s="64"/>
-      <c r="H207" s="64"/>
-      <c r="I207" s="91" t="s">
+      <c r="B207" s="54"/>
+      <c r="C207" s="54"/>
+      <c r="D207" s="54"/>
+      <c r="E207" s="54"/>
+      <c r="F207" s="54"/>
+      <c r="G207" s="54"/>
+      <c r="H207" s="54"/>
+      <c r="I207" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="J207" s="64"/>
-    </row>
-    <row r="208" spans="1:10" ht="12" customHeight="1">
+      <c r="J207" s="54"/>
+    </row>
+    <row r="208" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>4</v>
       </c>
@@ -7972,10 +7941,10 @@
       <c r="F208" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G208" s="75" t="s">
+      <c r="G208" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H208" s="75"/>
+      <c r="H208" s="85"/>
       <c r="I208" s="2" t="s">
         <v>11</v>
       </c>
@@ -7983,98 +7952,98 @@
         <v>12</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="12" customHeight="1">
-      <c r="A209" s="48" t="s">
+    <row r="209" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="37" t="s">
         <v>496</v>
       </c>
-      <c r="B209" s="51">
+      <c r="B209" s="39">
         <v>1</v>
       </c>
-      <c r="C209" s="52" t="s">
+      <c r="C209" s="40" t="s">
         <v>128</v>
       </c>
       <c r="D209" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E209" s="46" t="s">
+      <c r="E209" s="30" t="s">
         <v>192</v>
       </c>
       <c r="F209" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="G209" s="85" t="s">
+      <c r="G209" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="H209" s="86"/>
-      <c r="I209" s="46" t="s">
+      <c r="H209" s="82"/>
+      <c r="I209" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="J209" s="46" t="s">
+      <c r="J209" s="30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="12" customHeight="1">
-      <c r="A210" s="48" t="s">
+    <row r="210" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="37" t="s">
         <v>500</v>
       </c>
-      <c r="B210" s="51">
+      <c r="B210" s="39">
         <v>2</v>
       </c>
-      <c r="C210" s="52" t="s">
+      <c r="C210" s="40" t="s">
         <v>498</v>
       </c>
       <c r="D210" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E210" s="46" t="s">
+      <c r="E210" s="30" t="s">
         <v>200</v>
       </c>
       <c r="F210" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="G210" s="85" t="s">
+      <c r="G210" s="81" t="s">
         <v>499</v>
       </c>
-      <c r="H210" s="86"/>
-      <c r="I210" s="46" t="s">
+      <c r="H210" s="82"/>
+      <c r="I210" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="J210" s="46" t="s">
+      <c r="J210" s="30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="12" customHeight="1">
-      <c r="A211" s="48" t="s">
+    <row r="211" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="37" t="s">
         <v>507</v>
       </c>
-      <c r="B211" s="51">
+      <c r="B211" s="39">
         <v>3</v>
       </c>
-      <c r="C211" s="52" t="s">
+      <c r="C211" s="40" t="s">
         <v>503</v>
       </c>
       <c r="D211" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E211" s="46" t="s">
+      <c r="E211" s="30" t="s">
         <v>235</v>
       </c>
       <c r="F211" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="G211" s="85" t="s">
+      <c r="G211" s="81" t="s">
         <v>504</v>
       </c>
-      <c r="H211" s="86"/>
-      <c r="I211" s="46" t="s">
+      <c r="H211" s="82"/>
+      <c r="I211" s="30" t="s">
         <v>505</v>
       </c>
-      <c r="J211" s="46" t="s">
+      <c r="J211" s="30" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="12" customHeight="1">
-      <c r="A212" s="48" t="s">
+    <row r="212" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="37" t="s">
         <v>512</v>
       </c>
       <c r="B212" s="4">
@@ -8086,16 +8055,16 @@
       <c r="D212" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E212" s="46" t="s">
+      <c r="E212" s="30" t="s">
         <v>228</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G212" s="70" t="s">
+      <c r="G212" s="58" t="s">
         <v>511</v>
       </c>
-      <c r="H212" s="71"/>
+      <c r="H212" s="59"/>
       <c r="I212" s="7" t="s">
         <v>139</v>
       </c>
@@ -8103,316 +8072,316 @@
         <v>140</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="12" customHeight="1">
-      <c r="A213" s="48" t="s">
+    <row r="213" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="37" t="s">
         <v>515</v>
       </c>
-      <c r="B213" s="51">
+      <c r="B213" s="39">
         <v>5</v>
       </c>
-      <c r="C213" s="52" t="s">
+      <c r="C213" s="40" t="s">
         <v>131</v>
       </c>
       <c r="D213" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="E213" s="46" t="s">
+      <c r="E213" s="30" t="s">
         <v>198</v>
       </c>
       <c r="F213" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="G213" s="85" t="s">
+      <c r="G213" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="H213" s="86"/>
-      <c r="I213" s="46" t="s">
+      <c r="H213" s="82"/>
+      <c r="I213" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="J213" s="46" t="s">
+      <c r="J213" s="30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="12" customHeight="1">
-      <c r="A214" s="48" t="s">
+    <row r="214" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="37" t="s">
         <v>517</v>
       </c>
-      <c r="B214" s="51">
+      <c r="B214" s="39">
         <v>6</v>
       </c>
-      <c r="C214" s="52" t="s">
+      <c r="C214" s="40" t="s">
         <v>137</v>
       </c>
       <c r="D214" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E214" s="46" t="s">
+      <c r="E214" s="30" t="s">
         <v>225</v>
       </c>
       <c r="F214" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="G214" s="85" t="s">
+      <c r="G214" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="H214" s="86"/>
-      <c r="I214" s="46" t="s">
+      <c r="H214" s="82"/>
+      <c r="I214" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="J214" s="46" t="s">
+      <c r="J214" s="30" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="12" customHeight="1" thickBot="1">
-      <c r="A215" s="54" t="s">
+    <row r="215" spans="1:10" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A215" s="42" t="s">
         <v>519</v>
       </c>
       <c r="B215" s="9">
         <v>7</v>
       </c>
-      <c r="C215" s="58" t="s">
+      <c r="C215" s="46" t="s">
         <v>520</v>
       </c>
       <c r="D215" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E215" s="47" t="s">
+      <c r="E215" s="32" t="s">
         <v>199</v>
       </c>
       <c r="F215" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="G215" s="87" t="s">
+      <c r="G215" s="99" t="s">
         <v>521</v>
       </c>
-      <c r="H215" s="88"/>
-      <c r="I215" s="47" t="s">
+      <c r="H215" s="95"/>
+      <c r="I215" s="32" t="s">
         <v>522</v>
       </c>
-      <c r="J215" s="47" t="s">
+      <c r="J215" s="32" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="12" customHeight="1">
+    <row r="216" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>1</v>
       </c>
-      <c r="B216" s="80" t="s">
+      <c r="B216" s="66" t="s">
         <v>143</v>
       </c>
-      <c r="C216" s="62"/>
-      <c r="D216" s="62"/>
-      <c r="E216" s="62"/>
-      <c r="F216" s="62"/>
-      <c r="G216" s="80" t="s">
+      <c r="C216" s="57"/>
+      <c r="D216" s="57"/>
+      <c r="E216" s="57"/>
+      <c r="F216" s="57"/>
+      <c r="G216" s="66" t="s">
         <v>497</v>
       </c>
-      <c r="H216" s="62"/>
-      <c r="I216" s="62"/>
-      <c r="J216" s="62"/>
-    </row>
-    <row r="217" spans="1:10" ht="12" customHeight="1">
+      <c r="H216" s="57"/>
+      <c r="I216" s="57"/>
+      <c r="J216" s="57"/>
+    </row>
+    <row r="217" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>2</v>
       </c>
-      <c r="B217" s="80" t="s">
+      <c r="B217" s="66" t="s">
         <v>501</v>
       </c>
-      <c r="C217" s="62"/>
-      <c r="D217" s="62"/>
-      <c r="E217" s="62"/>
-      <c r="F217" s="62"/>
-      <c r="G217" s="80" t="s">
+      <c r="C217" s="57"/>
+      <c r="D217" s="57"/>
+      <c r="E217" s="57"/>
+      <c r="F217" s="57"/>
+      <c r="G217" s="66" t="s">
         <v>502</v>
       </c>
-      <c r="H217" s="62"/>
-      <c r="I217" s="62"/>
-      <c r="J217" s="62"/>
-    </row>
-    <row r="218" spans="1:10" ht="12" customHeight="1">
+      <c r="H217" s="57"/>
+      <c r="I217" s="57"/>
+      <c r="J217" s="57"/>
+    </row>
+    <row r="218" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>3</v>
       </c>
-      <c r="B218" s="80" t="s">
+      <c r="B218" s="66" t="s">
         <v>508</v>
       </c>
-      <c r="C218" s="62"/>
-      <c r="D218" s="62"/>
-      <c r="E218" s="62"/>
-      <c r="F218" s="62"/>
-      <c r="G218" s="80" t="s">
+      <c r="C218" s="57"/>
+      <c r="D218" s="57"/>
+      <c r="E218" s="57"/>
+      <c r="F218" s="57"/>
+      <c r="G218" s="66" t="s">
         <v>509</v>
       </c>
-      <c r="H218" s="62"/>
-      <c r="I218" s="62"/>
-      <c r="J218" s="62"/>
-    </row>
-    <row r="219" spans="1:10" ht="12" customHeight="1">
+      <c r="H218" s="57"/>
+      <c r="I218" s="57"/>
+      <c r="J218" s="57"/>
+    </row>
+    <row r="219" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>4</v>
       </c>
-      <c r="B219" s="80" t="s">
+      <c r="B219" s="66" t="s">
         <v>513</v>
       </c>
-      <c r="C219" s="62"/>
-      <c r="D219" s="62"/>
-      <c r="E219" s="62"/>
-      <c r="F219" s="62"/>
-      <c r="G219" s="80" t="s">
+      <c r="C219" s="57"/>
+      <c r="D219" s="57"/>
+      <c r="E219" s="57"/>
+      <c r="F219" s="57"/>
+      <c r="G219" s="66" t="s">
         <v>514</v>
       </c>
-      <c r="H219" s="62"/>
-      <c r="I219" s="62"/>
-      <c r="J219" s="62"/>
-    </row>
-    <row r="220" spans="1:10" ht="12" customHeight="1">
+      <c r="H219" s="57"/>
+      <c r="I219" s="57"/>
+      <c r="J219" s="57"/>
+    </row>
+    <row r="220" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>5</v>
       </c>
-      <c r="B220" s="80" t="s">
+      <c r="B220" s="66" t="s">
         <v>144</v>
       </c>
-      <c r="C220" s="62"/>
-      <c r="D220" s="62"/>
-      <c r="E220" s="62"/>
-      <c r="F220" s="62"/>
-      <c r="G220" s="80" t="s">
+      <c r="C220" s="57"/>
+      <c r="D220" s="57"/>
+      <c r="E220" s="57"/>
+      <c r="F220" s="57"/>
+      <c r="G220" s="66" t="s">
         <v>516</v>
       </c>
-      <c r="H220" s="62"/>
-      <c r="I220" s="62"/>
-      <c r="J220" s="62"/>
-    </row>
-    <row r="221" spans="1:10" ht="12" customHeight="1">
+      <c r="H220" s="57"/>
+      <c r="I220" s="57"/>
+      <c r="J220" s="57"/>
+    </row>
+    <row r="221" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>6</v>
       </c>
-      <c r="B221" s="80" t="s">
+      <c r="B221" s="66" t="s">
         <v>146</v>
       </c>
-      <c r="C221" s="62"/>
-      <c r="D221" s="62"/>
-      <c r="E221" s="62"/>
-      <c r="F221" s="62"/>
-      <c r="G221" s="80" t="s">
+      <c r="C221" s="57"/>
+      <c r="D221" s="57"/>
+      <c r="E221" s="57"/>
+      <c r="F221" s="57"/>
+      <c r="G221" s="66" t="s">
         <v>518</v>
       </c>
-      <c r="H221" s="62"/>
-      <c r="I221" s="62"/>
-      <c r="J221" s="62"/>
-    </row>
-    <row r="222" spans="1:10" ht="12" customHeight="1" thickBot="1">
+      <c r="H221" s="57"/>
+      <c r="I221" s="57"/>
+      <c r="J221" s="57"/>
+    </row>
+    <row r="222" spans="1:10" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="9">
-        <v>9</v>
-      </c>
-      <c r="B222" s="83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B222" s="90" t="s">
         <v>523</v>
       </c>
       <c r="C222" s="84"/>
       <c r="D222" s="84"/>
       <c r="E222" s="84"/>
       <c r="F222" s="84"/>
-      <c r="G222" s="83" t="s">
+      <c r="G222" s="90" t="s">
         <v>524</v>
       </c>
       <c r="H222" s="84"/>
       <c r="I222" s="84"/>
       <c r="J222" s="84"/>
     </row>
-    <row r="223" spans="1:10" ht="3" customHeight="1"/>
-    <row r="224" spans="1:10" ht="18.75">
-      <c r="A224" s="66" t="s">
+    <row r="223" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" spans="1:10" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="A224" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="B224" s="64"/>
-      <c r="C224" s="63" t="s">
+      <c r="B224" s="54"/>
+      <c r="C224" s="68" t="s">
         <v>494</v>
       </c>
-      <c r="D224" s="64"/>
-      <c r="E224" s="64"/>
-      <c r="F224" s="64"/>
-      <c r="G224" s="64"/>
-      <c r="H224" s="64"/>
-      <c r="I224" s="64"/>
-      <c r="J224" s="53" t="s">
+      <c r="D224" s="54"/>
+      <c r="E224" s="54"/>
+      <c r="F224" s="54"/>
+      <c r="G224" s="54"/>
+      <c r="H224" s="54"/>
+      <c r="I224" s="54"/>
+      <c r="J224" s="41" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="13.5" customHeight="1">
+    <row r="225" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="65" t="s">
         <v>159</v>
       </c>
-      <c r="B225" s="64"/>
-      <c r="C225" s="64"/>
-      <c r="D225" s="64"/>
-      <c r="E225" s="64"/>
-      <c r="F225" s="64"/>
-      <c r="G225" s="64"/>
-      <c r="H225" s="64"/>
-      <c r="I225" s="64"/>
-      <c r="J225" s="64"/>
-    </row>
-    <row r="226" spans="1:10" ht="11.25" customHeight="1">
-      <c r="A226" s="110" t="s">
+      <c r="B225" s="54"/>
+      <c r="C225" s="54"/>
+      <c r="D225" s="54"/>
+      <c r="E225" s="54"/>
+      <c r="F225" s="54"/>
+      <c r="G225" s="54"/>
+      <c r="H225" s="54"/>
+      <c r="I225" s="54"/>
+      <c r="J225" s="54"/>
+    </row>
+    <row r="226" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="86" t="s">
         <v>232</v>
       </c>
-      <c r="B226" s="64"/>
-      <c r="C226" s="64"/>
-      <c r="D226" s="64"/>
-      <c r="E226" s="64"/>
-      <c r="F226" s="64"/>
-      <c r="G226" s="64"/>
-      <c r="H226" s="64"/>
-      <c r="I226" s="64"/>
-      <c r="J226" s="64"/>
-    </row>
-    <row r="227" spans="1:10" ht="11.25" customHeight="1">
-      <c r="A227" s="110" t="s">
+      <c r="B226" s="54"/>
+      <c r="C226" s="54"/>
+      <c r="D226" s="54"/>
+      <c r="E226" s="54"/>
+      <c r="F226" s="54"/>
+      <c r="G226" s="54"/>
+      <c r="H226" s="54"/>
+      <c r="I226" s="54"/>
+      <c r="J226" s="54"/>
+    </row>
+    <row r="227" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="86" t="s">
         <v>231</v>
       </c>
-      <c r="B227" s="64"/>
-      <c r="C227" s="64"/>
-      <c r="D227" s="64"/>
-      <c r="E227" s="64"/>
-      <c r="F227" s="64"/>
-      <c r="G227" s="64"/>
-      <c r="H227" s="64"/>
-      <c r="I227" s="64"/>
-      <c r="J227" s="64"/>
-    </row>
-    <row r="228" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A228" s="92" t="s">
+      <c r="B227" s="54"/>
+      <c r="C227" s="54"/>
+      <c r="D227" s="54"/>
+      <c r="E227" s="54"/>
+      <c r="F227" s="54"/>
+      <c r="G227" s="54"/>
+      <c r="H227" s="54"/>
+      <c r="I227" s="54"/>
+      <c r="J227" s="54"/>
+    </row>
+    <row r="228" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="64" t="s">
         <v>233</v>
       </c>
-      <c r="B228" s="64"/>
-      <c r="C228" s="64"/>
-      <c r="D228" s="64"/>
-      <c r="E228" s="64"/>
-      <c r="F228" s="64"/>
-      <c r="G228" s="64"/>
-      <c r="H228" s="64"/>
-      <c r="I228" s="91" t="s">
+      <c r="B228" s="54"/>
+      <c r="C228" s="54"/>
+      <c r="D228" s="54"/>
+      <c r="E228" s="54"/>
+      <c r="F228" s="54"/>
+      <c r="G228" s="54"/>
+      <c r="H228" s="54"/>
+      <c r="I228" s="55" t="s">
         <v>189</v>
       </c>
-      <c r="J228" s="64"/>
-    </row>
-    <row r="229" spans="1:10" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A229" s="92" t="s">
+      <c r="J228" s="54"/>
+    </row>
+    <row r="229" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A229" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="B229" s="64"/>
-      <c r="C229" s="64"/>
-      <c r="D229" s="64"/>
-      <c r="E229" s="64"/>
-      <c r="F229" s="64"/>
-      <c r="G229" s="64"/>
-      <c r="H229" s="64"/>
-      <c r="I229" s="91" t="s">
+      <c r="B229" s="54"/>
+      <c r="C229" s="54"/>
+      <c r="D229" s="54"/>
+      <c r="E229" s="54"/>
+      <c r="F229" s="54"/>
+      <c r="G229" s="54"/>
+      <c r="H229" s="54"/>
+      <c r="I229" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="J229" s="64"/>
-    </row>
-    <row r="230" spans="1:10" ht="12" customHeight="1">
+      <c r="J229" s="54"/>
+    </row>
+    <row r="230" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>4</v>
       </c>
@@ -8431,10 +8400,10 @@
       <c r="F230" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G230" s="75" t="s">
+      <c r="G230" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H230" s="75"/>
+      <c r="H230" s="85"/>
       <c r="I230" s="2" t="s">
         <v>11</v>
       </c>
@@ -8442,68 +8411,68 @@
         <v>12</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="12" customHeight="1">
-      <c r="A231" s="59" t="s">
+    <row r="231" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="47" t="s">
         <v>525</v>
       </c>
-      <c r="B231" s="51">
+      <c r="B231" s="39">
         <v>1</v>
       </c>
-      <c r="C231" s="52" t="s">
+      <c r="C231" s="40" t="s">
         <v>163</v>
       </c>
       <c r="D231" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E231" s="46" t="s">
+      <c r="E231" s="30" t="s">
         <v>193</v>
       </c>
       <c r="F231" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="G231" s="85" t="s">
+      <c r="G231" s="81" t="s">
         <v>164</v>
       </c>
-      <c r="H231" s="86"/>
-      <c r="I231" s="46" t="s">
+      <c r="H231" s="82"/>
+      <c r="I231" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="J231" s="46" t="s">
+      <c r="J231" s="30" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="12" customHeight="1">
-      <c r="A232" s="48" t="s">
+    <row r="232" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="37" t="s">
         <v>530</v>
       </c>
-      <c r="B232" s="51">
+      <c r="B232" s="39">
         <v>2</v>
       </c>
-      <c r="C232" s="52" t="s">
+      <c r="C232" s="40" t="s">
         <v>527</v>
       </c>
       <c r="D232" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E232" s="46" t="s">
+      <c r="E232" s="30" t="s">
         <v>528</v>
       </c>
       <c r="F232" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="G232" s="85" t="s">
+      <c r="G232" s="81" t="s">
         <v>529</v>
       </c>
-      <c r="H232" s="86"/>
-      <c r="I232" s="46" t="s">
+      <c r="H232" s="82"/>
+      <c r="I232" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="J232" s="46" t="s">
+      <c r="J232" s="30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="12" customHeight="1">
-      <c r="A233" s="48" t="s">
+    <row r="233" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="37" t="s">
         <v>535</v>
       </c>
       <c r="B233" s="4">
@@ -8515,16 +8484,16 @@
       <c r="D233" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E233" s="46" t="s">
+      <c r="E233" s="30" t="s">
         <v>200</v>
       </c>
       <c r="F233" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G233" s="70" t="s">
+      <c r="G233" s="58" t="s">
         <v>534</v>
       </c>
-      <c r="H233" s="71"/>
+      <c r="H233" s="59"/>
       <c r="I233" s="7" t="s">
         <v>85</v>
       </c>
@@ -8532,68 +8501,68 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="12" customHeight="1">
-      <c r="A234" s="59" t="s">
+    <row r="234" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="47" t="s">
         <v>538</v>
       </c>
-      <c r="B234" s="51">
+      <c r="B234" s="39">
         <v>4</v>
       </c>
-      <c r="C234" s="52" t="s">
+      <c r="C234" s="40" t="s">
         <v>168</v>
       </c>
       <c r="D234" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E234" s="46" t="s">
+      <c r="E234" s="30" t="s">
         <v>235</v>
       </c>
       <c r="F234" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="G234" s="85" t="s">
+      <c r="G234" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="H234" s="86"/>
-      <c r="I234" s="46" t="s">
+      <c r="H234" s="82"/>
+      <c r="I234" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="J234" s="46" t="s">
+      <c r="J234" s="30" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="12" customHeight="1">
-      <c r="A235" s="48" t="s">
+    <row r="235" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="37" t="s">
         <v>542</v>
       </c>
-      <c r="B235" s="51">
+      <c r="B235" s="39">
         <v>5</v>
       </c>
-      <c r="C235" s="52" t="s">
+      <c r="C235" s="40" t="s">
         <v>540</v>
       </c>
       <c r="D235" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="E235" s="46" t="s">
+      <c r="E235" s="30" t="s">
         <v>191</v>
       </c>
       <c r="F235" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="G235" s="85" t="s">
+      <c r="G235" s="81" t="s">
         <v>541</v>
       </c>
-      <c r="H235" s="86"/>
-      <c r="I235" s="46" t="s">
+      <c r="H235" s="82"/>
+      <c r="I235" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="J235" s="46" t="s">
+      <c r="J235" s="30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="12" customHeight="1">
-      <c r="A236" s="48" t="s">
+    <row r="236" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="37" t="s">
         <v>549</v>
       </c>
       <c r="B236" s="4">
@@ -8605,16 +8574,16 @@
       <c r="D236" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E236" s="46" t="s">
+      <c r="E236" s="30" t="s">
         <v>236</v>
       </c>
       <c r="F236" s="31" t="s">
         <v>550</v>
       </c>
-      <c r="G236" s="70" t="s">
+      <c r="G236" s="58" t="s">
         <v>547</v>
       </c>
-      <c r="H236" s="71"/>
+      <c r="H236" s="59"/>
       <c r="I236" s="7" t="s">
         <v>16</v>
       </c>
@@ -8622,260 +8591,260 @@
         <v>548</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="12" customHeight="1">
+    <row r="237" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="8" t="s">
         <v>553</v>
       </c>
       <c r="B237" s="9">
         <v>7</v>
       </c>
-      <c r="C237" s="58" t="s">
+      <c r="C237" s="46" t="s">
         <v>554</v>
       </c>
       <c r="D237" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="E237" s="47" t="s">
+      <c r="E237" s="32" t="s">
         <v>561</v>
       </c>
       <c r="F237" s="33" t="s">
         <v>555</v>
       </c>
-      <c r="G237" s="87" t="s">
+      <c r="G237" s="99" t="s">
         <v>556</v>
       </c>
-      <c r="H237" s="88"/>
-      <c r="I237" s="47" t="s">
+      <c r="H237" s="95"/>
+      <c r="I237" s="32" t="s">
         <v>557</v>
       </c>
-      <c r="J237" s="47" t="s">
+      <c r="J237" s="32" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="12" customHeight="1">
+    <row r="238" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>1</v>
       </c>
-      <c r="B238" s="80" t="s">
+      <c r="B238" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="C238" s="62"/>
-      <c r="D238" s="62"/>
-      <c r="E238" s="62"/>
-      <c r="F238" s="62"/>
-      <c r="G238" s="80" t="s">
+      <c r="C238" s="57"/>
+      <c r="D238" s="57"/>
+      <c r="E238" s="57"/>
+      <c r="F238" s="57"/>
+      <c r="G238" s="66" t="s">
         <v>526</v>
       </c>
-      <c r="H238" s="62"/>
-      <c r="I238" s="62"/>
-      <c r="J238" s="62"/>
-    </row>
-    <row r="239" spans="1:10" ht="12" customHeight="1">
+      <c r="H238" s="57"/>
+      <c r="I238" s="57"/>
+      <c r="J238" s="57"/>
+    </row>
+    <row r="239" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>2</v>
       </c>
-      <c r="B239" s="80" t="s">
+      <c r="B239" s="66" t="s">
         <v>531</v>
       </c>
-      <c r="C239" s="62"/>
-      <c r="D239" s="62"/>
-      <c r="E239" s="62"/>
-      <c r="F239" s="62"/>
-      <c r="G239" s="80" t="s">
+      <c r="C239" s="57"/>
+      <c r="D239" s="57"/>
+      <c r="E239" s="57"/>
+      <c r="F239" s="57"/>
+      <c r="G239" s="66" t="s">
         <v>532</v>
       </c>
-      <c r="H239" s="62"/>
-      <c r="I239" s="62"/>
-      <c r="J239" s="62"/>
-    </row>
-    <row r="240" spans="1:10" ht="12" customHeight="1">
+      <c r="H239" s="57"/>
+      <c r="I239" s="57"/>
+      <c r="J239" s="57"/>
+    </row>
+    <row r="240" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>3</v>
       </c>
-      <c r="B240" s="80" t="s">
+      <c r="B240" s="66" t="s">
         <v>536</v>
       </c>
-      <c r="C240" s="62"/>
-      <c r="D240" s="62"/>
-      <c r="E240" s="62"/>
-      <c r="F240" s="62"/>
-      <c r="G240" s="80" t="s">
+      <c r="C240" s="57"/>
+      <c r="D240" s="57"/>
+      <c r="E240" s="57"/>
+      <c r="F240" s="57"/>
+      <c r="G240" s="66" t="s">
         <v>537</v>
       </c>
-      <c r="H240" s="62"/>
-      <c r="I240" s="62"/>
-      <c r="J240" s="62"/>
-    </row>
-    <row r="241" spans="1:10" ht="12" customHeight="1">
+      <c r="H240" s="57"/>
+      <c r="I240" s="57"/>
+      <c r="J240" s="57"/>
+    </row>
+    <row r="241" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>4</v>
       </c>
-      <c r="B241" s="80" t="s">
+      <c r="B241" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="C241" s="62"/>
-      <c r="D241" s="62"/>
-      <c r="E241" s="62"/>
-      <c r="F241" s="62"/>
-      <c r="G241" s="80" t="s">
+      <c r="C241" s="57"/>
+      <c r="D241" s="57"/>
+      <c r="E241" s="57"/>
+      <c r="F241" s="57"/>
+      <c r="G241" s="66" t="s">
         <v>539</v>
       </c>
-      <c r="H241" s="62"/>
-      <c r="I241" s="62"/>
-      <c r="J241" s="62"/>
-    </row>
-    <row r="242" spans="1:10" ht="12" customHeight="1">
+      <c r="H241" s="57"/>
+      <c r="I241" s="57"/>
+      <c r="J241" s="57"/>
+    </row>
+    <row r="242" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>5</v>
       </c>
-      <c r="B242" s="80" t="s">
+      <c r="B242" s="66" t="s">
         <v>543</v>
       </c>
-      <c r="C242" s="62"/>
-      <c r="D242" s="62"/>
-      <c r="E242" s="62"/>
-      <c r="F242" s="62"/>
-      <c r="G242" s="80" t="s">
+      <c r="C242" s="57"/>
+      <c r="D242" s="57"/>
+      <c r="E242" s="57"/>
+      <c r="F242" s="57"/>
+      <c r="G242" s="66" t="s">
         <v>544</v>
       </c>
-      <c r="H242" s="62"/>
-      <c r="I242" s="62"/>
-      <c r="J242" s="62"/>
-    </row>
-    <row r="243" spans="1:10" ht="12" customHeight="1">
+      <c r="H242" s="57"/>
+      <c r="I242" s="57"/>
+      <c r="J242" s="57"/>
+    </row>
+    <row r="243" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>6</v>
       </c>
-      <c r="B243" s="80" t="s">
+      <c r="B243" s="66" t="s">
         <v>551</v>
       </c>
-      <c r="C243" s="62"/>
-      <c r="D243" s="62"/>
-      <c r="E243" s="62"/>
-      <c r="F243" s="62"/>
-      <c r="G243" s="80" t="s">
+      <c r="C243" s="57"/>
+      <c r="D243" s="57"/>
+      <c r="E243" s="57"/>
+      <c r="F243" s="57"/>
+      <c r="G243" s="66" t="s">
         <v>552</v>
       </c>
-      <c r="H243" s="62"/>
-      <c r="I243" s="62"/>
-      <c r="J243" s="62"/>
-    </row>
-    <row r="244" spans="1:10" ht="12" customHeight="1" thickBot="1">
+      <c r="H243" s="57"/>
+      <c r="I243" s="57"/>
+      <c r="J243" s="57"/>
+    </row>
+    <row r="244" spans="1:10" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="9">
         <v>7</v>
       </c>
-      <c r="B244" s="83" t="s">
+      <c r="B244" s="90" t="s">
         <v>558</v>
       </c>
       <c r="C244" s="84"/>
       <c r="D244" s="84"/>
       <c r="E244" s="84"/>
       <c r="F244" s="84"/>
-      <c r="G244" s="83" t="s">
+      <c r="G244" s="90" t="s">
         <v>559</v>
       </c>
       <c r="H244" s="84"/>
       <c r="I244" s="84"/>
       <c r="J244" s="84"/>
     </row>
-    <row r="245" spans="1:10" s="34" customFormat="1" ht="3" customHeight="1">
-      <c r="A245" s="35"/>
-      <c r="B245" s="36"/>
-      <c r="C245" s="37"/>
-      <c r="D245" s="37"/>
-      <c r="E245" s="37"/>
-      <c r="F245" s="37"/>
-      <c r="G245" s="36"/>
-      <c r="H245" s="37"/>
-      <c r="I245" s="37"/>
-      <c r="J245" s="37"/>
-    </row>
-    <row r="246" spans="1:10" ht="18.75">
-      <c r="A246" s="66" t="s">
+    <row r="245" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="34"/>
+      <c r="B245" s="35"/>
+      <c r="C245" s="36"/>
+      <c r="D245" s="36"/>
+      <c r="E245" s="36"/>
+      <c r="F245" s="36"/>
+      <c r="G245" s="35"/>
+      <c r="H245" s="36"/>
+      <c r="I245" s="36"/>
+      <c r="J245" s="36"/>
+    </row>
+    <row r="246" spans="1:10" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="A246" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="B246" s="64"/>
-      <c r="C246" s="63" t="s">
+      <c r="B246" s="54"/>
+      <c r="C246" s="68" t="s">
         <v>605</v>
       </c>
-      <c r="D246" s="64"/>
-      <c r="E246" s="64"/>
-      <c r="F246" s="64"/>
-      <c r="G246" s="64"/>
-      <c r="H246" s="64"/>
-      <c r="I246" s="64"/>
-      <c r="J246" s="53" t="s">
+      <c r="D246" s="54"/>
+      <c r="E246" s="54"/>
+      <c r="F246" s="54"/>
+      <c r="G246" s="54"/>
+      <c r="H246" s="54"/>
+      <c r="I246" s="54"/>
+      <c r="J246" s="41" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="B247" s="64"/>
-      <c r="C247" s="64"/>
-      <c r="D247" s="64"/>
-      <c r="E247" s="64"/>
-      <c r="F247" s="64"/>
-      <c r="G247" s="64"/>
-      <c r="H247" s="64"/>
-      <c r="I247" s="64"/>
-      <c r="J247" s="64"/>
-    </row>
-    <row r="248" spans="1:10" ht="11.25" customHeight="1">
-      <c r="A248" s="96" t="s">
+      <c r="B247" s="54"/>
+      <c r="C247" s="54"/>
+      <c r="D247" s="54"/>
+      <c r="E247" s="54"/>
+      <c r="F247" s="54"/>
+      <c r="G247" s="54"/>
+      <c r="H247" s="54"/>
+      <c r="I247" s="54"/>
+      <c r="J247" s="54"/>
+    </row>
+    <row r="248" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="53" t="s">
         <v>573</v>
       </c>
-      <c r="B248" s="64"/>
-      <c r="C248" s="64"/>
-      <c r="D248" s="64"/>
-      <c r="E248" s="64"/>
-      <c r="F248" s="64"/>
-      <c r="G248" s="64"/>
-      <c r="H248" s="64"/>
-      <c r="I248" s="64"/>
-      <c r="J248" s="64"/>
-    </row>
-    <row r="249" spans="1:10" ht="11.25" customHeight="1">
-      <c r="A249" s="96" t="s">
+      <c r="B248" s="54"/>
+      <c r="C248" s="54"/>
+      <c r="D248" s="54"/>
+      <c r="E248" s="54"/>
+      <c r="F248" s="54"/>
+      <c r="G248" s="54"/>
+      <c r="H248" s="54"/>
+      <c r="I248" s="54"/>
+      <c r="J248" s="54"/>
+    </row>
+    <row r="249" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="53" t="s">
         <v>574</v>
       </c>
-      <c r="B249" s="64"/>
-      <c r="C249" s="64"/>
-      <c r="D249" s="64"/>
-      <c r="E249" s="64"/>
-      <c r="F249" s="64"/>
-      <c r="G249" s="64"/>
-      <c r="H249" s="64"/>
-      <c r="I249" s="64"/>
-      <c r="J249" s="64"/>
-    </row>
-    <row r="250" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A250" s="92" t="s">
+      <c r="B249" s="54"/>
+      <c r="C249" s="54"/>
+      <c r="D249" s="54"/>
+      <c r="E249" s="54"/>
+      <c r="F249" s="54"/>
+      <c r="G249" s="54"/>
+      <c r="H249" s="54"/>
+      <c r="I249" s="54"/>
+      <c r="J249" s="54"/>
+    </row>
+    <row r="250" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="B250" s="64"/>
-      <c r="C250" s="64"/>
-      <c r="D250" s="64"/>
-      <c r="E250" s="64"/>
-      <c r="F250" s="64"/>
-      <c r="G250" s="64"/>
-      <c r="H250" s="64"/>
+      <c r="B250" s="54"/>
+      <c r="C250" s="54"/>
+      <c r="D250" s="54"/>
+      <c r="E250" s="54"/>
+      <c r="F250" s="54"/>
+      <c r="G250" s="54"/>
+      <c r="H250" s="54"/>
       <c r="I250" s="29"/>
     </row>
-    <row r="251" spans="1:10" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A251" s="92" t="s">
+    <row r="251" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A251" s="64" t="s">
         <v>229</v>
       </c>
-      <c r="B251" s="64"/>
-      <c r="C251" s="64"/>
-      <c r="D251" s="64"/>
-      <c r="E251" s="64"/>
-      <c r="F251" s="64"/>
-      <c r="G251" s="64"/>
-      <c r="H251" s="64"/>
-    </row>
-    <row r="252" spans="1:10" ht="12" customHeight="1">
+      <c r="B251" s="54"/>
+      <c r="C251" s="54"/>
+      <c r="D251" s="54"/>
+      <c r="E251" s="54"/>
+      <c r="F251" s="54"/>
+      <c r="G251" s="54"/>
+      <c r="H251" s="54"/>
+    </row>
+    <row r="252" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>4</v>
       </c>
@@ -8894,10 +8863,10 @@
       <c r="F252" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G252" s="75" t="s">
+      <c r="G252" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H252" s="75"/>
+      <c r="H252" s="85"/>
       <c r="I252" s="2" t="s">
         <v>11</v>
       </c>
@@ -8905,380 +8874,380 @@
         <v>12</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="12" customHeight="1">
-      <c r="A253" s="48" t="s">
+    <row r="253" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="37" t="s">
         <v>565</v>
       </c>
-      <c r="B253" s="51">
+      <c r="B253" s="39">
         <v>1</v>
       </c>
-      <c r="C253" s="52" t="s">
+      <c r="C253" s="40" t="s">
         <v>562</v>
       </c>
       <c r="D253" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="E253" s="46" t="s">
+      <c r="E253" s="30" t="s">
         <v>199</v>
       </c>
       <c r="F253" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="G253" s="85" t="s">
+      <c r="G253" s="81" t="s">
         <v>563</v>
       </c>
-      <c r="H253" s="86"/>
-      <c r="I253" s="46" t="s">
+      <c r="H253" s="82"/>
+      <c r="I253" s="30" t="s">
         <v>564</v>
       </c>
-      <c r="J253" s="46" t="s">
+      <c r="J253" s="30" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="12" customHeight="1">
-      <c r="A254" s="48" t="s">
+    <row r="254" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="37" t="s">
         <v>569</v>
       </c>
-      <c r="B254" s="51">
+      <c r="B254" s="39">
         <v>2</v>
       </c>
-      <c r="C254" s="52" t="s">
+      <c r="C254" s="40" t="s">
         <v>151</v>
       </c>
       <c r="D254" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E254" s="46" t="s">
+      <c r="E254" s="30" t="s">
         <v>200</v>
       </c>
       <c r="F254" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="G254" s="85" t="s">
+      <c r="G254" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="H254" s="86"/>
-      <c r="I254" s="46" t="s">
+      <c r="H254" s="82"/>
+      <c r="I254" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="J254" s="46" t="s">
+      <c r="J254" s="30" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="255" spans="1:10" ht="12" customHeight="1">
-      <c r="A255" s="48" t="s">
+    <row r="255" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="37" t="s">
         <v>571</v>
       </c>
-      <c r="B255" s="51">
+      <c r="B255" s="39">
         <v>3</v>
       </c>
-      <c r="C255" s="52" t="s">
+      <c r="C255" s="40" t="s">
         <v>83</v>
       </c>
       <c r="D255" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E255" s="46" t="s">
+      <c r="E255" s="30" t="s">
         <v>546</v>
       </c>
       <c r="F255" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="G255" s="85" t="s">
+      <c r="G255" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="H255" s="86"/>
-      <c r="I255" s="46" t="s">
+      <c r="H255" s="82"/>
+      <c r="I255" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="J255" s="46" t="s">
+      <c r="J255" s="30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="12" customHeight="1">
-      <c r="A256" s="48" t="s">
+    <row r="256" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="37" t="s">
         <v>577</v>
       </c>
-      <c r="B256" s="51">
+      <c r="B256" s="39">
         <v>4</v>
       </c>
-      <c r="C256" s="52" t="s">
+      <c r="C256" s="40" t="s">
         <v>575</v>
       </c>
       <c r="D256" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E256" s="46"/>
+      <c r="E256" s="30"/>
       <c r="F256" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="G256" s="85" t="s">
+      <c r="G256" s="81" t="s">
         <v>576</v>
       </c>
-      <c r="H256" s="86"/>
-      <c r="I256" s="46" t="s">
+      <c r="H256" s="82"/>
+      <c r="I256" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="J256" s="46" t="s">
+      <c r="J256" s="30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="12" customHeight="1">
-      <c r="A257" s="48" t="s">
+    <row r="257" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="37" t="s">
         <v>580</v>
       </c>
-      <c r="B257" s="51">
+      <c r="B257" s="39">
         <v>5</v>
       </c>
-      <c r="C257" s="52" t="s">
+      <c r="C257" s="40" t="s">
         <v>86</v>
       </c>
       <c r="D257" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E257" s="46"/>
+      <c r="E257" s="30"/>
       <c r="F257" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="G257" s="85" t="s">
+      <c r="G257" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="H257" s="86"/>
-      <c r="I257" s="46" t="s">
+      <c r="H257" s="82"/>
+      <c r="I257" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="J257" s="46" t="s">
+      <c r="J257" s="30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="12" customHeight="1">
-      <c r="A258" s="48" t="s">
+    <row r="258" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="37" t="s">
         <v>592</v>
       </c>
       <c r="B258" s="4">
         <v>6</v>
       </c>
-      <c r="C258" s="52" t="s">
+      <c r="C258" s="40" t="s">
         <v>593</v>
       </c>
       <c r="D258" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="E258" s="46" t="s">
+      <c r="E258" s="30" t="s">
         <v>203</v>
       </c>
       <c r="F258" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="G258" s="85" t="s">
+      <c r="G258" s="81" t="s">
         <v>594</v>
       </c>
-      <c r="H258" s="71"/>
-      <c r="I258" s="46" t="s">
+      <c r="H258" s="59"/>
+      <c r="I258" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="J258" s="46" t="s">
+      <c r="J258" s="30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="12" customHeight="1">
-      <c r="A259" s="48" t="s">
+    <row r="259" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="37" t="s">
         <v>584</v>
       </c>
-      <c r="B259" s="51">
+      <c r="B259" s="39">
         <v>7</v>
       </c>
-      <c r="C259" s="52" t="s">
+      <c r="C259" s="40" t="s">
         <v>582</v>
       </c>
       <c r="D259" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E259" s="46" t="s">
+      <c r="E259" s="30" t="s">
         <v>235</v>
       </c>
       <c r="F259" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="G259" s="85" t="s">
+      <c r="G259" s="81" t="s">
         <v>583</v>
       </c>
-      <c r="H259" s="86"/>
-      <c r="I259" s="46" t="s">
+      <c r="H259" s="82"/>
+      <c r="I259" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="J259" s="46" t="s">
+      <c r="J259" s="30" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="12" customHeight="1" thickBot="1">
-      <c r="A260" s="54" t="s">
+    <row r="260" spans="1:10" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A260" s="42" t="s">
         <v>589</v>
       </c>
-      <c r="B260" s="60">
+      <c r="B260" s="48">
         <v>8</v>
       </c>
-      <c r="C260" s="58" t="s">
+      <c r="C260" s="46" t="s">
         <v>587</v>
       </c>
       <c r="D260" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E260" s="47" t="s">
+      <c r="E260" s="32" t="s">
         <v>204</v>
       </c>
       <c r="F260" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G260" s="87" t="s">
+      <c r="G260" s="99" t="s">
         <v>588</v>
       </c>
-      <c r="H260" s="109"/>
-      <c r="I260" s="47" t="s">
+      <c r="H260" s="100"/>
+      <c r="I260" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="J260" s="47" t="s">
+      <c r="J260" s="32" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="12" customHeight="1">
+    <row r="261" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>1</v>
       </c>
-      <c r="B261" s="80" t="s">
+      <c r="B261" s="66" t="s">
         <v>567</v>
       </c>
-      <c r="C261" s="62"/>
-      <c r="D261" s="62"/>
-      <c r="E261" s="62"/>
-      <c r="F261" s="62"/>
-      <c r="G261" s="80" t="s">
+      <c r="C261" s="57"/>
+      <c r="D261" s="57"/>
+      <c r="E261" s="57"/>
+      <c r="F261" s="57"/>
+      <c r="G261" s="66" t="s">
         <v>568</v>
       </c>
-      <c r="H261" s="62"/>
-      <c r="I261" s="62"/>
-      <c r="J261" s="62"/>
-    </row>
-    <row r="262" spans="1:10" ht="12" customHeight="1">
+      <c r="H261" s="57"/>
+      <c r="I261" s="57"/>
+      <c r="J261" s="57"/>
+    </row>
+    <row r="262" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>2</v>
       </c>
-      <c r="B262" s="80" t="s">
+      <c r="B262" s="66" t="s">
         <v>156</v>
       </c>
-      <c r="C262" s="62"/>
-      <c r="D262" s="62"/>
-      <c r="E262" s="62"/>
-      <c r="F262" s="62"/>
-      <c r="G262" s="80" t="s">
+      <c r="C262" s="57"/>
+      <c r="D262" s="57"/>
+      <c r="E262" s="57"/>
+      <c r="F262" s="57"/>
+      <c r="G262" s="66" t="s">
         <v>570</v>
       </c>
-      <c r="H262" s="62"/>
-      <c r="I262" s="62"/>
-      <c r="J262" s="62"/>
-    </row>
-    <row r="263" spans="1:10" ht="12" customHeight="1">
+      <c r="H262" s="57"/>
+      <c r="I262" s="57"/>
+      <c r="J262" s="57"/>
+    </row>
+    <row r="263" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>3</v>
       </c>
-      <c r="B263" s="80" t="s">
+      <c r="B263" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="C263" s="62"/>
-      <c r="D263" s="62"/>
-      <c r="E263" s="62"/>
-      <c r="F263" s="62"/>
-      <c r="G263" s="80" t="s">
+      <c r="C263" s="57"/>
+      <c r="D263" s="57"/>
+      <c r="E263" s="57"/>
+      <c r="F263" s="57"/>
+      <c r="G263" s="66" t="s">
         <v>572</v>
       </c>
-      <c r="H263" s="62"/>
-      <c r="I263" s="62"/>
-      <c r="J263" s="62"/>
-    </row>
-    <row r="264" spans="1:10" ht="12" customHeight="1">
+      <c r="H263" s="57"/>
+      <c r="I263" s="57"/>
+      <c r="J263" s="57"/>
+    </row>
+    <row r="264" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>4</v>
       </c>
-      <c r="B264" s="80" t="s">
+      <c r="B264" s="66" t="s">
         <v>578</v>
       </c>
-      <c r="C264" s="62"/>
-      <c r="D264" s="62"/>
-      <c r="E264" s="62"/>
-      <c r="F264" s="62"/>
-      <c r="G264" s="80" t="s">
+      <c r="C264" s="57"/>
+      <c r="D264" s="57"/>
+      <c r="E264" s="57"/>
+      <c r="F264" s="57"/>
+      <c r="G264" s="66" t="s">
         <v>579</v>
       </c>
-      <c r="H264" s="62"/>
-      <c r="I264" s="62"/>
-      <c r="J264" s="62"/>
-    </row>
-    <row r="265" spans="1:10" ht="12" customHeight="1">
+      <c r="H264" s="57"/>
+      <c r="I264" s="57"/>
+      <c r="J264" s="57"/>
+    </row>
+    <row r="265" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>5</v>
       </c>
-      <c r="B265" s="80" t="s">
+      <c r="B265" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="C265" s="62"/>
-      <c r="D265" s="62"/>
-      <c r="E265" s="62"/>
-      <c r="F265" s="62"/>
-      <c r="G265" s="80" t="s">
+      <c r="C265" s="57"/>
+      <c r="D265" s="57"/>
+      <c r="E265" s="57"/>
+      <c r="F265" s="57"/>
+      <c r="G265" s="66" t="s">
         <v>581</v>
       </c>
-      <c r="H265" s="62"/>
-      <c r="I265" s="62"/>
-      <c r="J265" s="62"/>
-    </row>
-    <row r="266" spans="1:10" ht="12" customHeight="1">
+      <c r="H265" s="57"/>
+      <c r="I265" s="57"/>
+      <c r="J265" s="57"/>
+    </row>
+    <row r="266" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>6</v>
       </c>
-      <c r="B266" s="80" t="s">
+      <c r="B266" s="66" t="s">
         <v>596</v>
       </c>
-      <c r="C266" s="62"/>
-      <c r="D266" s="62"/>
-      <c r="E266" s="62"/>
-      <c r="F266" s="62"/>
-      <c r="G266" s="80" t="s">
+      <c r="C266" s="57"/>
+      <c r="D266" s="57"/>
+      <c r="E266" s="57"/>
+      <c r="F266" s="57"/>
+      <c r="G266" s="66" t="s">
         <v>595</v>
       </c>
-      <c r="H266" s="62"/>
-      <c r="I266" s="62"/>
-      <c r="J266" s="62"/>
-    </row>
-    <row r="267" spans="1:10" ht="12" customHeight="1">
+      <c r="H266" s="57"/>
+      <c r="I266" s="57"/>
+      <c r="J266" s="57"/>
+    </row>
+    <row r="267" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>7</v>
       </c>
-      <c r="B267" s="80" t="s">
+      <c r="B267" s="66" t="s">
         <v>585</v>
       </c>
-      <c r="C267" s="62"/>
-      <c r="D267" s="62"/>
-      <c r="E267" s="62"/>
-      <c r="F267" s="62"/>
-      <c r="G267" s="80" t="s">
+      <c r="C267" s="57"/>
+      <c r="D267" s="57"/>
+      <c r="E267" s="57"/>
+      <c r="F267" s="57"/>
+      <c r="G267" s="66" t="s">
         <v>586</v>
       </c>
-      <c r="H267" s="62"/>
-      <c r="I267" s="62"/>
-      <c r="J267" s="62"/>
-    </row>
-    <row r="268" spans="1:10" ht="12" customHeight="1" thickBot="1">
+      <c r="H267" s="57"/>
+      <c r="I267" s="57"/>
+      <c r="J267" s="57"/>
+    </row>
+    <row r="268" spans="1:10" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="9">
         <v>8</v>
       </c>
-      <c r="B268" s="83" t="s">
+      <c r="B268" s="90" t="s">
         <v>590</v>
       </c>
       <c r="C268" s="84"/>
       <c r="D268" s="84"/>
       <c r="E268" s="84"/>
       <c r="F268" s="84"/>
-      <c r="G268" s="83" t="s">
+      <c r="G268" s="90" t="s">
         <v>591</v>
       </c>
       <c r="H268" s="84"/>
@@ -9286,10 +9255,341 @@
       <c r="J268" s="84"/>
     </row>
   </sheetData>
-  <sortState ref="A55:J63">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A55:J63">
     <sortCondition ref="B55:B63"/>
   </sortState>
   <mergeCells count="355">
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="C48:I48"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A126:B126"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="G132:H132"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G116:J116"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="G119:J119"/>
+    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="G120:J120"/>
+    <mergeCell ref="B121:F121"/>
+    <mergeCell ref="G121:J121"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="G64:J64"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="G122:J122"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="G118:J118"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="A94:J94"/>
+    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="G112:J112"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="G268:J268"/>
+    <mergeCell ref="G216:J216"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G90:J90"/>
+    <mergeCell ref="G240:J240"/>
+    <mergeCell ref="B218:F218"/>
+    <mergeCell ref="G242:J242"/>
+    <mergeCell ref="C179:I179"/>
+    <mergeCell ref="B242:F242"/>
+    <mergeCell ref="G134:H134"/>
+    <mergeCell ref="G136:H136"/>
+    <mergeCell ref="B240:F240"/>
+    <mergeCell ref="G89:J89"/>
+    <mergeCell ref="G192:H192"/>
+    <mergeCell ref="G237:H237"/>
+    <mergeCell ref="G231:H231"/>
+    <mergeCell ref="B263:F263"/>
+    <mergeCell ref="G86:J86"/>
+    <mergeCell ref="I184:J184"/>
+    <mergeCell ref="G168:H168"/>
+    <mergeCell ref="G117:J117"/>
+    <mergeCell ref="B244:F244"/>
+    <mergeCell ref="I162:J162"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="A162:H162"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="G150:J150"/>
+    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G72:J72"/>
+    <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="G87:J87"/>
+    <mergeCell ref="B176:F176"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G71:J71"/>
+    <mergeCell ref="B151:F151"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G144:J144"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="G141:H141"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B261:F261"/>
+    <mergeCell ref="G171:J171"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G234:H234"/>
+    <mergeCell ref="B239:F239"/>
+    <mergeCell ref="G254:H254"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="B117:F117"/>
+    <mergeCell ref="G209:H209"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="A182:J182"/>
+    <mergeCell ref="G173:J173"/>
+    <mergeCell ref="A184:H184"/>
+    <mergeCell ref="G238:J238"/>
+    <mergeCell ref="A247:J247"/>
+    <mergeCell ref="A249:J249"/>
+    <mergeCell ref="G235:H235"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="B216:F216"/>
+    <mergeCell ref="G257:H257"/>
+    <mergeCell ref="A248:J248"/>
+    <mergeCell ref="G243:J243"/>
+    <mergeCell ref="G208:H208"/>
+    <mergeCell ref="G172:J172"/>
+    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="G154:J154"/>
+    <mergeCell ref="A160:J160"/>
+    <mergeCell ref="A158:J158"/>
+    <mergeCell ref="G165:H165"/>
+    <mergeCell ref="G253:H253"/>
+    <mergeCell ref="G197:J197"/>
+    <mergeCell ref="G220:J220"/>
+    <mergeCell ref="A207:H207"/>
+    <mergeCell ref="G236:H236"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="A224:B224"/>
+    <mergeCell ref="G212:H212"/>
+    <mergeCell ref="G232:H232"/>
+    <mergeCell ref="G211:H211"/>
+    <mergeCell ref="B219:F219"/>
+    <mergeCell ref="A229:H229"/>
+    <mergeCell ref="G222:J222"/>
+    <mergeCell ref="A251:H251"/>
+    <mergeCell ref="G145:J145"/>
+    <mergeCell ref="I207:J207"/>
+    <mergeCell ref="B175:F175"/>
+    <mergeCell ref="B171:F171"/>
+    <mergeCell ref="I183:J183"/>
+    <mergeCell ref="G152:J152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="G153:J153"/>
+    <mergeCell ref="A250:H250"/>
+    <mergeCell ref="G166:H166"/>
+    <mergeCell ref="A159:J159"/>
+    <mergeCell ref="G233:H233"/>
+    <mergeCell ref="G164:H164"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="G174:J174"/>
+    <mergeCell ref="G214:H214"/>
+    <mergeCell ref="G149:J149"/>
+    <mergeCell ref="G151:J151"/>
+    <mergeCell ref="I228:J228"/>
+    <mergeCell ref="A225:J225"/>
+    <mergeCell ref="A227:J227"/>
+    <mergeCell ref="G221:J221"/>
+    <mergeCell ref="B243:F243"/>
+    <mergeCell ref="B264:F264"/>
+    <mergeCell ref="C157:I157"/>
+    <mergeCell ref="A228:H228"/>
+    <mergeCell ref="B266:F266"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="B201:F201"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="G215:H215"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B265:F265"/>
+    <mergeCell ref="G262:J262"/>
+    <mergeCell ref="G263:J263"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A246:B246"/>
+    <mergeCell ref="A161:H161"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="G170:H170"/>
+    <mergeCell ref="B238:F238"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="B262:F262"/>
+    <mergeCell ref="G218:J218"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="A203:B203"/>
+    <mergeCell ref="B172:F172"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="G169:H169"/>
+    <mergeCell ref="G193:H193"/>
+    <mergeCell ref="G191:H191"/>
+    <mergeCell ref="G114:J114"/>
+    <mergeCell ref="G177:J177"/>
+    <mergeCell ref="G115:J115"/>
+    <mergeCell ref="G199:J199"/>
+    <mergeCell ref="G137:H137"/>
+    <mergeCell ref="G185:H185"/>
+    <mergeCell ref="G198:J198"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="G176:J176"/>
+    <mergeCell ref="G186:H186"/>
+    <mergeCell ref="G139:H139"/>
+    <mergeCell ref="G256:H256"/>
+    <mergeCell ref="B268:F268"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="G113:J113"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="G195:J195"/>
+    <mergeCell ref="A127:J127"/>
+    <mergeCell ref="G217:J217"/>
+    <mergeCell ref="G65:J65"/>
+    <mergeCell ref="B145:F145"/>
+    <mergeCell ref="G196:J196"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="G67:J67"/>
+    <mergeCell ref="G219:J219"/>
+    <mergeCell ref="G189:H189"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="G259:H259"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="G66:J66"/>
+    <mergeCell ref="B222:F222"/>
+    <mergeCell ref="C246:I246"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B267:F267"/>
+    <mergeCell ref="G188:H188"/>
+    <mergeCell ref="G190:H190"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="G69:J69"/>
+    <mergeCell ref="B241:F241"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="B220:F220"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="G244:J244"/>
+    <mergeCell ref="G175:J175"/>
+    <mergeCell ref="G167:H167"/>
+    <mergeCell ref="G187:H187"/>
+    <mergeCell ref="I206:J206"/>
+    <mergeCell ref="G155:J155"/>
+    <mergeCell ref="C224:I224"/>
+    <mergeCell ref="G210:H210"/>
+    <mergeCell ref="G138:H138"/>
+    <mergeCell ref="I130:J130"/>
+    <mergeCell ref="G239:J239"/>
+    <mergeCell ref="G241:J241"/>
+    <mergeCell ref="G230:H230"/>
+    <mergeCell ref="G260:H260"/>
+    <mergeCell ref="G201:J201"/>
+    <mergeCell ref="A206:H206"/>
+    <mergeCell ref="A183:H183"/>
+    <mergeCell ref="A179:B179"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A204:J204"/>
+    <mergeCell ref="C74:I74"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="G91:J91"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="C126:I126"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A128:J128"/>
+    <mergeCell ref="B199:F199"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G200:J200"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B200:F200"/>
+    <mergeCell ref="B198:F198"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="G147:J147"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="G265:J265"/>
+    <mergeCell ref="G255:H255"/>
+    <mergeCell ref="B148:F148"/>
+    <mergeCell ref="G267:J267"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="G261:J261"/>
+    <mergeCell ref="G258:H258"/>
+    <mergeCell ref="G266:J266"/>
+    <mergeCell ref="G252:H252"/>
+    <mergeCell ref="B197:F197"/>
+    <mergeCell ref="B217:F217"/>
+    <mergeCell ref="G264:J264"/>
+    <mergeCell ref="I161:J161"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="I229:J229"/>
+    <mergeCell ref="G131:H131"/>
+    <mergeCell ref="A181:J181"/>
+    <mergeCell ref="G213:H213"/>
+    <mergeCell ref="G148:J148"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="G194:J194"/>
+    <mergeCell ref="A157:B157"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B196:F196"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="I6:J6"/>
@@ -9314,337 +9614,6 @@
     <mergeCell ref="G82:H82"/>
     <mergeCell ref="C93:I93"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="G265:J265"/>
-    <mergeCell ref="G255:H255"/>
-    <mergeCell ref="B148:F148"/>
-    <mergeCell ref="G267:J267"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="G261:J261"/>
-    <mergeCell ref="G258:H258"/>
-    <mergeCell ref="G266:J266"/>
-    <mergeCell ref="G252:H252"/>
-    <mergeCell ref="B197:F197"/>
-    <mergeCell ref="B217:F217"/>
-    <mergeCell ref="G264:J264"/>
-    <mergeCell ref="I161:J161"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="I229:J229"/>
-    <mergeCell ref="G131:H131"/>
-    <mergeCell ref="A181:J181"/>
-    <mergeCell ref="G213:H213"/>
-    <mergeCell ref="G148:J148"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="G194:J194"/>
-    <mergeCell ref="A157:B157"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B196:F196"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="G200:J200"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="B116:F116"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="B195:F195"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B200:F200"/>
-    <mergeCell ref="B198:F198"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="G107:H107"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="G109:H109"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="G147:J147"/>
-    <mergeCell ref="B155:F155"/>
-    <mergeCell ref="G201:J201"/>
-    <mergeCell ref="A206:H206"/>
-    <mergeCell ref="A183:H183"/>
-    <mergeCell ref="A179:B179"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A204:J204"/>
-    <mergeCell ref="C74:I74"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="G91:J91"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="A49:J49"/>
-    <mergeCell ref="C126:I126"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="B267:F267"/>
-    <mergeCell ref="G188:H188"/>
-    <mergeCell ref="G190:H190"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="G69:J69"/>
-    <mergeCell ref="B241:F241"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="B220:F220"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="G244:J244"/>
-    <mergeCell ref="G175:J175"/>
-    <mergeCell ref="G167:H167"/>
-    <mergeCell ref="G187:H187"/>
-    <mergeCell ref="I206:J206"/>
-    <mergeCell ref="G155:J155"/>
-    <mergeCell ref="C224:I224"/>
-    <mergeCell ref="G210:H210"/>
-    <mergeCell ref="G138:H138"/>
-    <mergeCell ref="I130:J130"/>
-    <mergeCell ref="G239:J239"/>
-    <mergeCell ref="G241:J241"/>
-    <mergeCell ref="G230:H230"/>
-    <mergeCell ref="G260:H260"/>
-    <mergeCell ref="G256:H256"/>
-    <mergeCell ref="B268:F268"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="G113:J113"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="G195:J195"/>
-    <mergeCell ref="A127:J127"/>
-    <mergeCell ref="G217:J217"/>
-    <mergeCell ref="G65:J65"/>
-    <mergeCell ref="B145:F145"/>
-    <mergeCell ref="G196:J196"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="G67:J67"/>
-    <mergeCell ref="G219:J219"/>
-    <mergeCell ref="G189:H189"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="G259:H259"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="G66:J66"/>
-    <mergeCell ref="B222:F222"/>
-    <mergeCell ref="C246:I246"/>
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="A128:J128"/>
-    <mergeCell ref="B199:F199"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="A129:H129"/>
-    <mergeCell ref="A130:H130"/>
-    <mergeCell ref="A203:B203"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="G143:H143"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="G135:H135"/>
-    <mergeCell ref="G169:H169"/>
-    <mergeCell ref="G193:H193"/>
-    <mergeCell ref="G191:H191"/>
-    <mergeCell ref="G114:J114"/>
-    <mergeCell ref="G177:J177"/>
-    <mergeCell ref="G115:J115"/>
-    <mergeCell ref="G199:J199"/>
-    <mergeCell ref="G137:H137"/>
-    <mergeCell ref="G185:H185"/>
-    <mergeCell ref="G198:J198"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="G176:J176"/>
-    <mergeCell ref="G186:H186"/>
-    <mergeCell ref="B264:F264"/>
-    <mergeCell ref="C157:I157"/>
-    <mergeCell ref="A228:H228"/>
-    <mergeCell ref="B266:F266"/>
-    <mergeCell ref="B91:F91"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="B201:F201"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="G215:H215"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B194:F194"/>
-    <mergeCell ref="B265:F265"/>
-    <mergeCell ref="G262:J262"/>
-    <mergeCell ref="G263:J263"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A246:B246"/>
-    <mergeCell ref="A161:H161"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="G170:H170"/>
-    <mergeCell ref="B238:F238"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="B262:F262"/>
-    <mergeCell ref="G218:J218"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="G139:H139"/>
-    <mergeCell ref="A251:H251"/>
-    <mergeCell ref="G145:J145"/>
-    <mergeCell ref="I207:J207"/>
-    <mergeCell ref="B175:F175"/>
-    <mergeCell ref="B171:F171"/>
-    <mergeCell ref="I183:J183"/>
-    <mergeCell ref="G152:J152"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="G153:J153"/>
-    <mergeCell ref="A250:H250"/>
-    <mergeCell ref="G166:H166"/>
-    <mergeCell ref="A159:J159"/>
-    <mergeCell ref="G233:H233"/>
-    <mergeCell ref="G164:H164"/>
-    <mergeCell ref="B221:F221"/>
-    <mergeCell ref="G174:J174"/>
-    <mergeCell ref="G214:H214"/>
-    <mergeCell ref="G149:J149"/>
-    <mergeCell ref="G151:J151"/>
-    <mergeCell ref="I228:J228"/>
-    <mergeCell ref="A225:J225"/>
-    <mergeCell ref="A227:J227"/>
-    <mergeCell ref="G221:J221"/>
-    <mergeCell ref="B243:F243"/>
-    <mergeCell ref="G208:H208"/>
-    <mergeCell ref="G172:J172"/>
-    <mergeCell ref="B154:F154"/>
-    <mergeCell ref="G154:J154"/>
-    <mergeCell ref="A160:J160"/>
-    <mergeCell ref="A158:J158"/>
-    <mergeCell ref="G165:H165"/>
-    <mergeCell ref="G253:H253"/>
-    <mergeCell ref="G197:J197"/>
-    <mergeCell ref="G220:J220"/>
-    <mergeCell ref="A207:H207"/>
-    <mergeCell ref="G236:H236"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="A224:B224"/>
-    <mergeCell ref="G212:H212"/>
-    <mergeCell ref="G232:H232"/>
-    <mergeCell ref="G211:H211"/>
-    <mergeCell ref="B219:F219"/>
-    <mergeCell ref="A229:H229"/>
-    <mergeCell ref="G222:J222"/>
-    <mergeCell ref="B261:F261"/>
-    <mergeCell ref="G171:J171"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="G234:H234"/>
-    <mergeCell ref="B239:F239"/>
-    <mergeCell ref="G254:H254"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="B117:F117"/>
-    <mergeCell ref="G209:H209"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="A182:J182"/>
-    <mergeCell ref="G173:J173"/>
-    <mergeCell ref="A184:H184"/>
-    <mergeCell ref="G238:J238"/>
-    <mergeCell ref="A247:J247"/>
-    <mergeCell ref="A249:J249"/>
-    <mergeCell ref="G235:H235"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="B216:F216"/>
-    <mergeCell ref="G257:H257"/>
-    <mergeCell ref="A248:J248"/>
-    <mergeCell ref="G243:J243"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G133:H133"/>
-    <mergeCell ref="A162:H162"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="G150:J150"/>
-    <mergeCell ref="G70:J70"/>
-    <mergeCell ref="G72:J72"/>
-    <mergeCell ref="A180:J180"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="G87:J87"/>
-    <mergeCell ref="B176:F176"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G71:J71"/>
-    <mergeCell ref="B151:F151"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="G144:J144"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="G141:H141"/>
-    <mergeCell ref="G142:H142"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="G268:J268"/>
-    <mergeCell ref="G216:J216"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="G90:J90"/>
-    <mergeCell ref="G240:J240"/>
-    <mergeCell ref="B218:F218"/>
-    <mergeCell ref="G242:J242"/>
-    <mergeCell ref="C179:I179"/>
-    <mergeCell ref="B242:F242"/>
-    <mergeCell ref="G134:H134"/>
-    <mergeCell ref="G136:H136"/>
-    <mergeCell ref="B240:F240"/>
-    <mergeCell ref="G89:J89"/>
-    <mergeCell ref="G192:H192"/>
-    <mergeCell ref="G237:H237"/>
-    <mergeCell ref="G231:H231"/>
-    <mergeCell ref="B263:F263"/>
-    <mergeCell ref="G86:J86"/>
-    <mergeCell ref="I184:J184"/>
-    <mergeCell ref="G168:H168"/>
-    <mergeCell ref="G117:J117"/>
-    <mergeCell ref="B244:F244"/>
-    <mergeCell ref="I162:J162"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="A51:J51"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="G118:J118"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="A94:J94"/>
-    <mergeCell ref="B112:F112"/>
-    <mergeCell ref="G112:J112"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="C48:I48"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A126:B126"/>
-    <mergeCell ref="B71:F71"/>
-    <mergeCell ref="G132:H132"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G116:J116"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="G119:J119"/>
-    <mergeCell ref="B120:F120"/>
-    <mergeCell ref="G120:J120"/>
-    <mergeCell ref="B121:F121"/>
-    <mergeCell ref="G121:J121"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="G64:J64"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="G122:J122"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="G123:J123"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
